--- a/Deliverables/Phase2/Sprint2/asvs/v4-ASVS-checklist-en.xlsx
+++ b/Deliverables/Phase2/Sprint2/asvs/v4-ASVS-checklist-en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29010"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myisepipp-my.sharepoint.com/personal/1191938_isep_ipp_pt/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7870FAD4-7935-49C1-A2AD-092E61DB18CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AB99EDA-0FD6-4AE3-9ECF-5C1701685BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="12" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="6804" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="6" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASVS Results" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="872">
   <si>
     <t>Security Category</t>
   </si>
@@ -688,6 +688,12 @@
     <t>Verify that anti-automation controls are effective at mitigating breached credential testing, brute force, and account lockout attacks. Such controls include blocking the most common breached passwords, soft lockouts, rate limiting, CAPTCHA, ever increasing delays between attempts, IP address restrictions, or risk-based restrictions such as location, first login on a device, recent attempts to unlock the account, or similar. Verify that no more than 100 failed attempts per hour is possible on a single account.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/api/AuthApi.java</t>
+  </si>
+  <si>
+    <t>Use ip to see if it exceds the number of times defined and if it yes it blocks the user.</t>
+  </si>
+  <si>
     <t>2.2.2</t>
   </si>
   <si>
@@ -778,12 +784,21 @@
     <t>Verify that passwords are stored in a form that is resistant to offline attacks. Passwords SHALL be salted and hashed using an approved one-way key derivation or password hashing function. Key derivation and password hashing functions take a password, a salt, and a cost factor as inputs when generating a password hash. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/usermanagement/services/UserService.java</t>
+  </si>
+  <si>
+    <t>line 126</t>
+  </si>
+  <si>
     <t>2.4.2</t>
   </si>
   <si>
     <t>Verify that the salt is at least 32 bits in length and be chosen arbitrarily to minimize salt value collisions among stored hashes. For each credential, a unique salt value and the resulting hash SHALL be stored. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>line 233. BCryptPasswordEncoder already generates a 128 bit salt</t>
+  </si>
+  <si>
     <t>2.4.3</t>
   </si>
   <si>
@@ -796,6 +811,9 @@
     <t>Verify that if bcrypt is used, the work factor SHOULD be as large as verification server performance will allow, with a minimum of 10. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>line 233. BCryptPasswordEncoder by default as a work facto of 10</t>
+  </si>
+  <si>
     <t>2.4.5</t>
   </si>
   <si>
@@ -823,12 +841,18 @@
     <t>Verify password credential recovery does not reveal the current password in any way. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>It asks for the previous passoword but doenst show it</t>
+  </si>
+  <si>
     <t>2.5.4</t>
   </si>
   <si>
     <t>Verify shared or default accounts are not present (e.g. "root", "admin", or "sa").</t>
   </si>
   <si>
+    <t>Changed the bootstrap so it no longer creates a admin account</t>
+  </si>
+  <si>
     <t>2.5.5</t>
   </si>
   <si>
@@ -838,6 +862,12 @@
     <t>Verify that if an authentication factor is changed or replaced, that the user is notified of this event.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/usermanagement/api/UserController.java</t>
+  </si>
+  <si>
+    <t>User is notified when password is changed.Line 133-138</t>
+  </si>
+  <si>
     <t>2.5.6</t>
   </si>
   <si>
@@ -1018,6 +1048,9 @@
     <t>Verify that if passwords are required for service authentication, the service account used is not a default credential. (e.g. root/root or admin/admin are default in some services during installation).</t>
   </si>
   <si>
+    <t>No default password are used like admin,root etc..</t>
+  </si>
+  <si>
     <t>2.10.3</t>
   </si>
   <si>
@@ -1039,6 +1072,9 @@
     <t>Verify the application never reveals session tokens in URL parameters or error messages.</t>
   </si>
   <si>
+    <t>It is used generic message witout much information</t>
+  </si>
+  <si>
     <t>Session Binding</t>
   </si>
   <si>
@@ -1048,24 +1084,39 @@
     <t>Verify the application generates a new session token on user authentication. ([C6](https://www.owasp.org/index.php/OWASP_Proactive_Controls#tab=Formal_Numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/configuration/JwtService.java</t>
+  </si>
+  <si>
+    <t>The application generates a new JWT (JSON Web Token) upon each user authentication. This token has a maximum validity of 10 minutes</t>
+  </si>
+  <si>
     <t>3.2.2</t>
   </si>
   <si>
     <t>Verify that session tokens possess at least 64 bits of entropy. ([C6](https://www.owasp.org/index.php/OWASP_Proactive_Controls#tab=Formal_Numbering))</t>
   </si>
   <si>
+    <t>The system uses RSA-signed JWTs with cryptographically secure keys, ensuring each token exceeds the 64-bit entropy requirement. Line 206-210</t>
+  </si>
+  <si>
     <t>3.2.3</t>
   </si>
   <si>
     <t>Verify the application only stores session tokens in the browser using secure methods such as appropriately secured cookies (see section 3.4) or HTML 5 session storage.</t>
   </si>
   <si>
+    <t>No front-end</t>
+  </si>
+  <si>
     <t>3.2.4</t>
   </si>
   <si>
     <t>Verify that session tokens are generated using approved cryptographic algorithms. ([C6](https://www.owasp.org/index.php/OWASP_Proactive_Controls#tab=Formal_Numbering))</t>
   </si>
   <si>
+    <t>The application generates JWT tokens using the RSA algorithm via the Nimbus JOSE+JWT library, which is an OWASP-approved cryptographic standard for secure token generation. Line 209</t>
+  </si>
+  <si>
     <t>Session Termination</t>
   </si>
   <si>
@@ -1073,6 +1124,9 @@
   </si>
   <si>
     <t>Verify that logout and expiration invalidate the session token, such that the back button or a downstream relying party does not resume an authenticated session, including across relying parties. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
+  </si>
+  <si>
+    <t>No logout</t>
   </si>
   <si>
     <t>3.3.2</t>
@@ -1084,6 +1138,9 @@
 * L3: 12 hours or 15 minutes of inactivity, with 2FA</t>
   </si>
   <si>
+    <t>Expires after 10 minutos.Line 43</t>
+  </si>
+  <si>
     <t>3.3.3</t>
   </si>
   <si>
@@ -1108,6 +1165,9 @@
     <t>Verify that cookie-based session tokens have the 'Secure' attribute set. ([C6](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>No Front-end</t>
+  </si>
+  <si>
     <t>3.4.2</t>
   </si>
   <si>
@@ -1144,18 +1204,28 @@
     <t>Verify the application allows users to revoke OAuth tokens that form trust relationships with linked applications.</t>
   </si>
   <si>
+    <t xml:space="preserve">Our application does not currently use OAuth or support third-party integrations. All authentication is handled internally using JWT tokens. </t>
+  </si>
+  <si>
     <t>3.5.2</t>
   </si>
   <si>
     <t>Verify the application uses session tokens rather than static API secrets and keys, except with legacy implementations.</t>
   </si>
   <si>
+    <t xml:space="preserve">We use JWT tokens instead of static API keys because they are more secure, support short lifespans, and don't require storing secrets on the server. </t>
+  </si>
+  <si>
     <t>3.5.3</t>
   </si>
   <si>
     <t>Verify that stateless session tokens use digital signatures, encryption, and other countermeasures to protect against tampering, enveloping, replay, null cipher, and key substitution attacks.</t>
   </si>
   <si>
+    <t xml:space="preserve">The JWT tokens are digitally signed with RSA keys, preventing tampering and ensuring token integrity. This meets the requirement for protecting stateless session tokens against common attacks.
+</t>
+  </si>
+  <si>
     <t>Federated Re-authentication</t>
   </si>
   <si>
@@ -1183,6 +1253,9 @@
     <t>Verify the application ensures a valid login session or requires re-authentication or secondary verification before allowing any sensitive transactions or account modifications.</t>
   </si>
   <si>
+    <t>This code makes sure only a logged-in user can do sensitive actions by always getting the user from the current login session (getCurrentAuthenticatedUser() method, around line 263)</t>
+  </si>
+  <si>
     <t>General Access Control Design</t>
   </si>
   <si>
@@ -1282,9 +1355,6 @@
     <t>Verify that the application has defenses against HTTP parameter pollution attacks, particularly if the application framework makes no distinction about the source of request parameters (GET, POST, cookies, headers, or environment variables).</t>
   </si>
   <si>
-    <t>There is distinction betwen the request type</t>
-  </si>
-  <si>
     <t>5.1.2</t>
   </si>
   <si>
@@ -1324,18 +1394,12 @@
     <t>Verify that URL redirects and forwards only allow destinations which appear on an allow list, or show a warning when redirecting to potentially untrusted content.</t>
   </si>
   <si>
-    <t>No redirect in application</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sanitization and Sandboxing </t>
   </si>
   <si>
     <t>Verify that all untrusted HTML input from WYSIWYG editors or similar is properly sanitized with an HTML sanitizer library or framework feature. ([C5](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t>No frontend</t>
-  </si>
-  <si>
     <t>5.2.2</t>
   </si>
   <si>
@@ -1351,22 +1415,25 @@
     <t>Verify that the application sanitizes user input before passing to mail systems to protect against SMTP or IMAP injection.</t>
   </si>
   <si>
-    <t>No mail server</t>
-  </si>
-  <si>
     <t>5.2.4</t>
   </si>
   <si>
     <t>Verify that the application avoids the use of eval() or other dynamic code execution features. Where there is no alternative, any user input being included must be sanitized or sandboxed before being executed.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/filestoragemanagement/sanitize/SanitizeImage.java</t>
+  </si>
+  <si>
+    <t>Application blocks all command injection patterns (|, &amp;, ;, $) and search confirms zero eval/Runtime/ScriptEngine usage - SanitizeImage.java</t>
+  </si>
+  <si>
     <t>Verify that the application protects against template injection attacks by ensuring that any user input being included is sanitized or sandboxed.</t>
   </si>
   <si>
+    <t>Uses RBAC,JWT tokens</t>
+  </si>
+  <si>
     <t>Verify that the application protects against SSRF attacks, by validating or sanitizing untrusted data or HTTP file metadata, such as filenames and URL input fields, and uses allow lists of protocols, domains, paths and ports.</t>
-  </si>
-  <si>
-    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/filestoragemanagement/sanitize/SanitizeImage.java</t>
   </si>
   <si>
     <t>Check if uploaded file doesn´t point to  remote  url</t>
@@ -1424,6 +1491,9 @@
     <t>Verify that output encoding preserves the user's chosen character set and locale, such that any Unicode character point is valid and safely handled. ([C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>This class validates file uploads while preserving Unicode character sets and locale.It filters only security-dangerous characters (path traversal, control chars) without altering the original UTF-8 encoding, ensuring user's chosen character set and locale remain intact throughout validation.</t>
+  </si>
+  <si>
     <t>5.3.3</t>
   </si>
   <si>
@@ -1449,36 +1519,24 @@
     <t>Verify that where parameterized or safer mechanisms are not present, context-specific output encoding is used to protect against injection attacks, such as the use of SQL escaping to protect against SQL injection. ([C3, C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t>Parameterized queries via Spring Data JPA are used, eliminating the need for manual SQL escaping.</t>
-  </si>
-  <si>
     <t>5.3.6</t>
   </si>
   <si>
     <t>Verify that the application protects against JSON injection attacks, JSON eval attacks, and JavaScript expression evaluation. ([C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t xml:space="preserve"> The application is backend-only using Spring Boot with no JavaScript-based JSON evaluation or dynamic code execution. the application is backend-only using Spring Boot with no JavaScript-based JSON evaluation or dynamic code execution.</t>
-  </si>
-  <si>
     <t>5.3.7</t>
   </si>
   <si>
     <t>Verify that the application protects against LDAP injection vulnerabilities, or that specific security controls to prevent LDAP injection have been implemented. ([C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t xml:space="preserve"> The application does not use LDAP or perform LDAP queries.</t>
-  </si>
-  <si>
     <t>5.3.8</t>
   </si>
   <si>
     <t>Verify that the application protects against OS command injection and that operating system calls use parameterized OS queries or use contextual command line output encoding. ([C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t>The application does not execute OS commands or shell calls; therefore, OS command injection risks are not present.</t>
-  </si>
-  <si>
     <t>5.3.9</t>
   </si>
   <si>
@@ -1494,6 +1552,9 @@
     <t>Verify that the application protects against XPath injection or XML injection attacks. ([C4](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>Prevents XML injection by blocking SVG uploads through strict image type whitelisting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Memory, String and Unmanaged Code </t>
   </si>
   <si>
@@ -1503,6 +1564,10 @@
     <t>Verify that the application uses memory-safe string, safer memory copy and pointer arithmetic to detect or prevent stack, buffer, or heap overflows.</t>
   </si>
   <si>
+    <t xml:space="preserve">The application is developed using a managed language (Java) which inherently provides memory safety and prevents buffer and heap overflows via its runtime environment.
+</t>
+  </si>
+  <si>
     <t>5.4.2</t>
   </si>
   <si>
@@ -1533,21 +1598,24 @@
     <t>Verify that the application correctly restricts XML parsers to only use the most restrictive configuration possible and to ensure that unsafe features such as resolving external entities are disabled to prevent XML eXternal Entity (XXE) attacks.</t>
   </si>
   <si>
+    <t> The application also uses Apache Tika for file type validation in SanitizeImage.java, providing defense-in-depth against file-based XXE attacks</t>
+  </si>
+  <si>
     <t>5.5.3</t>
   </si>
   <si>
     <t>Verify that deserialization of untrusted data is avoided or is protected in both custom code and third-party libraries (such as JSON, XML and YAML parsers).</t>
   </si>
   <si>
+    <t>All REST controllers use type-safe DTOs mapped through MapStruct, ensuring controlled deserialization paths without arbitrary object instantiation.</t>
+  </si>
+  <si>
     <t>5.5.4</t>
   </si>
   <si>
     <t>Verify that when parsing JSON in browsers or JavaScript-based backends, JSON.parse is used to parse the JSON document. Do not use eval() to parse JSON.</t>
   </si>
   <si>
-    <t>No frontend, no  Javascript based backend</t>
-  </si>
-  <si>
     <t>Data Classification</t>
   </si>
   <si>
@@ -1557,6 +1625,31 @@
     <t>Verify that regulated private data is stored encrypted while at rest, such as Personally Identifiable Information (PII), sensitive personal information, or data assessed likely to be subject to EU's GDPR.</t>
   </si>
   <si>
+    <t>"public String encrypt(String plaintext) {
+        if (plaintext == null || plaintext.isEmpty()) {
+            return plaintext;
+        }
+        try {
+            byte[] iv = new byte[ivLength];
+            secureRandom.nextBytes(iv);
+            Cipher cipher = Cipher.getInstance(transformation);
+            GCMParameterSpec gcmParameterSpec = new GCMParameterSpec(tagLength, iv);
+            cipher.init(Cipher.ENCRYPT_MODE, encryptionKey, gcmParameterSpec);
+            byte[] encryptedData = cipher.doFinal(plaintext.getBytes(StandardCharsets.UTF_8));
+            ByteBuffer buffer = ByteBuffer.allocate(ivLength + encryptedData.length);
+            buffer.put(iv);
+            buffer.put(encryptedData);
+            return Base64.getEncoder().encodeToString(buffer.array());
+        } catch (Exception e) {
+            logger.error("Encryption failed", e);
+            throw new RuntimeException("Failed to encrypt data", e);
+        }
+    }"</t>
+  </si>
+  <si>
+    <t>User location, email, phone number, and age are encrypted before being saved.</t>
+  </si>
+  <si>
     <t>6.1.2</t>
   </si>
   <si>
@@ -1575,48 +1668,118 @@
     <t>Verify that all cryptographic modules fail securely, and errors are handled in a way that does not enable Padding Oracle attacks.</t>
   </si>
   <si>
+    <t>Exceptions with generic error messages are used. Also, GCM is already resistant to Padding Oracle attacks.</t>
+  </si>
+  <si>
     <t>6.2.2</t>
   </si>
   <si>
     <t>Verify that industry proven or government approved cryptographic algorithms, modes, and libraries are used, instead of custom coded cryptography. ([C8](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/configuration/SecurityConfig.java "@Bean
+	 public PasswordEncoder passwordEncoder() {
+		return new BCryptPasswordEncoder();
+	}"</t>
+  </si>
+  <si>
+    <t>Bcrypt password encoder is used for password hashing, RSA algorithm is used for JWT encoding/decoding, and AES is used for user data encryption which are industry standard algorithms.</t>
+  </si>
+  <si>
     <t>6.2.3</t>
   </si>
   <si>
     <t>Verify that encryption initialization vector, cipher configuration, and block modes are configured securely using the latest advice.</t>
   </si>
   <si>
+    <t>AES/GCM is used, along with random generated IV for each encryption with SecureRandom.</t>
+  </si>
+  <si>
     <t>6.2.4</t>
   </si>
   <si>
     <t>Verify that random number, encryption or hashing algorithms, key lengths, rounds, ciphers or modes, can be reconfigured, upgraded, or swapped at any time, to protect against cryptographic breaks. ([C8](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/configuration/SecurityConfig.java @Bean
+	public JwtEncoder jwtEncoder() {
+		final JWK jwk = new RSAKey.Builder(this.rsaPublicKey).privateKey(this.rsaPrivateKey).build();
+		final JWKSource&lt;SecurityContext&gt; jwks = new ImmutableJWKSet&lt;&gt;(new JWKSet(jwk));
+		return new NimbusJwtEncoder(jwks);
+	}
+	// Used by JwtAuthenticationProvider to decode and validate JWT tokens
+	@Bean
+	public JwtDecoder jwtDecoder() {
+		return NimbusJwtDecoder.withPublicKey(this.rsaPublicKey).build();
+	}</t>
+  </si>
+  <si>
+    <t>The cryptographic primitives in use (BCrypt for password hashing and RSA for JWT signing) are configured via dependency injection and Spring beans in SecurityConfig.</t>
+  </si>
+  <si>
     <t>6.2.5</t>
   </si>
   <si>
     <t>Verify that known insecure block modes (i.e. ECB, etc.), padding modes (i.e. PKCS#1 v1.5, etc.), ciphers with small block sizes (i.e. Triple-DES, Blowfish, etc.), and weak hashing algorithms (i.e. MD5, SHA1, etc.) are not used unless required for backwards compatibility.</t>
   </si>
   <si>
+    <t>JWTs are signed with RSA keys via Nimbus JOSE JWT, which does not use insecure block modes like ECB or weak paddings. Passwords are hashed with BCrypt, which is a strong, industry-standard algorithm and does not use weak hash functions like MD5 or SHA1. For user data encryption, AES/GCM is used.</t>
+  </si>
+  <si>
     <t>6.2.6</t>
   </si>
   <si>
     <t>Verify that nonces, initialization vectors, and other single use numbers must not be used more than once with a given encryption key. The method of generation must be appropriate for the algorithm being used.</t>
   </si>
   <si>
+    <t>Passwords are protected with bcrypt, which generates a unique random salt for each password. This salt is treated as a single-use value (equivalent to a nonce) and is never reused. Also, a new IV is generated for each user data encription.</t>
+  </si>
+  <si>
     <t>6.2.7</t>
   </si>
   <si>
     <t>Verify that encrypted data is authenticated via signatures, authenticated cipher modes, or HMAC to ensure that ciphertext is not altered by an unauthorized party.</t>
   </si>
   <si>
+    <t>"@Bean
+	public JwtEncoder jwtEncoder() {
+		final JWK jwk = new RSAKey.Builder(this.rsaPublicKey).privateKey(this.rsaPrivateKey).build();
+		final JWKSource&lt;SecurityContext&gt; jwks = new ImmutableJWKSet&lt;&gt;(new JWKSet(jwk));
+		return new NimbusJwtEncoder(jwks);
+	}
+	// Used by JwtAuthenticationProvider to decode and validate JWT tokens
+	@Bean
+	public JwtDecoder jwtDecoder() {
+		return NimbusJwtDecoder.withPublicKey(this.rsaPublicKey).build();
+	}"</t>
+  </si>
+  <si>
+    <t>JWTs are signed (authenticated) using RSA, and GCM provides authenticated encription.</t>
+  </si>
+  <si>
     <t>6.2.8</t>
   </si>
   <si>
     <t>Verify that all cryptographic operations are constant-time, with no 'short-circuit' operations in comparisons, calculations, or returns, to avoid leaking information.</t>
   </si>
   <si>
+    <t>@Bean_x000D_
+	public JwtEncoder jwtEncoder() {_x000D_
+		final JWK jwk = new RSAKey.Builder(this.rsaPublicKey).privateKey(this.rsaPrivateKey).build();_x000D_
+		final JWKSource&lt;SecurityContext&gt; jwks = new ImmutableJWKSet&lt;&gt;(new JWKSet(jwk));_x000D_
+		return new NimbusJwtEncoder(jwks);_x000D_
+	}_x000D_
+_x000D_
+	// Used by JwtAuthenticationProvider to decode and validate JWT tokens_x000D_
+	@Bean_x000D_
+	public JwtDecoder jwtDecoder() {_x000D_
+		return NimbusJwtDecoder.withPublicKey(this.rsaPublicKey).build();_x000D_
+	}</t>
+  </si>
+  <si>
+    <t>All cryptographic operations (password hashing with BCrypt and JWT signing/verification with RSA via Nimbus JOSE JWT) are handled by well-established libraries.</t>
+  </si>
+  <si>
     <t>Random values</t>
   </si>
   <si>
@@ -1626,18 +1789,33 @@
     <t>Verify that all random numbers, random file names, random GUIDs, and random strings are generated using the cryptographic module's approved cryptographically secure random number generator when these random values are intended to be not guessable by an attacker.</t>
   </si>
   <si>
+    <t>"@Bean
+	public PasswordEncoder passwordEncoder() {
+		return new BCryptPasswordEncoder();
+	}"</t>
+  </si>
+  <si>
+    <t>The random salt used in password hashing is generated using a secure random number generator, managed by BCryptPasswordEncoder. Other random values are not security relevant.</t>
+  </si>
+  <si>
     <t>6.3.2</t>
   </si>
   <si>
     <t>Verify that random GUIDs are created using the GUID v4 algorithm, and a Cryptographically-secure Pseudo-random Number Generator (CSPRNG). GUIDs created using other pseudo-random number generators may be predictable.</t>
   </si>
   <si>
+    <t>Random UUIDs generated in the project are exclusively used for internal logging or files names that aren't externally accessible without authentication.</t>
+  </si>
+  <si>
     <t>6.3.3</t>
   </si>
   <si>
     <t>Verify that random numbers are created with proper entropy even when the application is under heavy load, or that the application degrades gracefully in such circumstances.</t>
   </si>
   <si>
+    <t>All cryptographic operations (password hashing with BCrypt and JWT signing/verification with RSA via Nimbus JOSE JWT) use, by default, Spring Security SecureRandom for random number generation.</t>
+  </si>
+  <si>
     <t>Secret Management</t>
   </si>
   <si>
@@ -1647,6 +1825,12 @@
     <t>Verify that a secrets management solution such as a key vault is used to securely create, store, control access to and destroy secrets. ([C8](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/.github/workflows/build_and_publish.yaml</t>
+  </si>
+  <si>
+    <t>Secrets are managed using GitHub Secrets</t>
+  </si>
+  <si>
     <t>6.4.2</t>
   </si>
   <si>
@@ -1659,9 +1843,6 @@
     <t>Verify that the application does not log credentials or payment details. Session tokens should only be stored in logs in an irreversible, hashed form. ([C9, C10](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
-    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/api/AuthApi.java</t>
-  </si>
-  <si>
     <t>Inside the try-catch block of the login method</t>
   </si>
   <si>
@@ -1785,12 +1966,21 @@
     <t>Verify the application minimizes the number of parameters in a request, such as hidden fields, Ajax variables, cookies and header values.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/dashboardmanagement/api/DashboardController.java</t>
+  </si>
+  <si>
+    <t>Parameter minimization - Controllers use minimal params with @Valid validation (DashboardController.getDashboardView max 6 params)</t>
+  </si>
+  <si>
     <t>8.1.4</t>
   </si>
   <si>
     <t>Verify the application can detect and alert on abnormal numbers of requests, such as by IP, user, total per hour or day, or whatever makes sense for the application.</t>
   </si>
   <si>
+    <t>The LoginAttemptService.loginFailed() in LoginAttemptService.java implements request monitoring by tracking attempt counts per user/IP, detecting threshold breaches (5 user, 20 IP), and triggering automatic blocks with security logging.</t>
+  </si>
+  <si>
     <t>8.1.5</t>
   </si>
   <si>
@@ -1872,6 +2062,9 @@
     <t>Verify that sensitive or private information that is required to be encrypted, is encrypted using approved algorithms that provide both confidentiality and integrity. ([C8](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/usermanagement/services/LoginAttemptService.java</t>
+  </si>
+  <si>
     <t>8.3.8</t>
   </si>
   <si>
@@ -2025,6 +2218,9 @@
     <t>Verify that the application employs integrity protections, such as code signing or subresource integrity. The application must not load or execute code from untrusted sources, such as loading includes, modules, plugins, code, or libraries from untrusted sources or the Internet.</t>
   </si>
   <si>
+    <t>SecurityConfig.java proves integrity protection through HTTPS enforcement, CSP headers blocking untrusted scripts, and strict access controls.</t>
+  </si>
+  <si>
     <t>10.3.3</t>
   </si>
   <si>
@@ -2034,7 +2230,7 @@
     <t xml:space="preserve">https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/resources/application.properties </t>
   </si>
   <si>
-    <t>application properties line 83 to 88</t>
+    <t>Application.properties line 83 to 88</t>
   </si>
   <si>
     <t>Business Logic Security Requirements</t>
@@ -2046,6 +2242,9 @@
     <t>Verify that the application will only process business logic flows for the same user in sequential step order and without skipping steps.</t>
   </si>
   <si>
+    <t>This requirement is fulfilled by enforcing sequential business logic steps — such as plan selection, subscription creation, cancellation, renewal, and plan changes — while ensuring that only the authenticated user can perform these actions and that each step validates the current subscription state.</t>
+  </si>
+  <si>
     <t>11.1.2</t>
   </si>
   <si>
@@ -2112,19 +2311,28 @@
     <t>Verify that the application will not accept large files that could fill up storage or cause a denial of service.</t>
   </si>
   <si>
+    <t>Upload size limits are configured in application.properties to prevent large file uploads and mitigate DoS risks</t>
+  </si>
+  <si>
     <t>12.1.2</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that the application checks compressed files (e.g. zip, gz, docx, odt) against maximum allowed uncompressed size and against maximum number of files before uncompressing the file. </t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/filestoragemanagement/sanitize/AllowedImage.java</t>
+  </si>
+  <si>
+    <t>Application does not support/allow compressed files</t>
+  </si>
+  <si>
     <t>12.1.3</t>
   </si>
   <si>
     <t>Verify that a file size quota and maximum number of files per user is enforced to ensure that a single user cannot fill up the storage with too many files, or excessively large files.</t>
   </si>
   <si>
-    <t>A user can only have one image, however size is not validated</t>
+    <t>Lines 53 and 55. A user can only have one image</t>
   </si>
   <si>
     <t>File Integrity</t>
@@ -2136,6 +2344,9 @@
     <t>Verify that files obtained from untrusted sources are validated to be of expected type based on the file's content.</t>
   </si>
   <si>
+    <t>Lines 113 to 121</t>
+  </si>
+  <si>
     <t>File Execution</t>
   </si>
   <si>
@@ -2145,6 +2356,12 @@
     <t>Verify that user-submitted filename metadata is not used directly by system or framework filesystems and that a URL API is used to protect against path traversal.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/filestoragemanagement/sanitize/SanitizeImage.java#L87</t>
+  </si>
+  <si>
+    <t>Lines 87 to 111</t>
+  </si>
+  <si>
     <t>12.3.2</t>
   </si>
   <si>
@@ -2184,6 +2401,12 @@
     <t>Verify that files obtained from untrusted sources are stored outside the web root, with limited permissions.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/resources/assets/keep-calm-and-love-jpa.png</t>
+  </si>
+  <si>
+    <t>The files are stored in a specific folder outside the web root</t>
+  </si>
+  <si>
     <t>12.4.2</t>
   </si>
   <si>
@@ -2223,6 +2446,9 @@
     <t>Verify that all application components use the same encodings and parsers to avoid parsing attacks that exploit different URI or file parsing behavior that could be used in SSRF and RFI attacks.</t>
   </si>
   <si>
+    <t>This configuration ensures consistent encoding and parsing across all components by integrating the EncodingSecurityFilter for SSRF/RFI protection</t>
+  </si>
+  <si>
     <t>13.1.2</t>
   </si>
   <si>
@@ -2289,6 +2515,9 @@
     <t>Verify that REST services explicitly check the incoming Content-Type to be the expected one, such as application/xml or application/json.</t>
   </si>
   <si>
+    <t>Uses @PostMapping, @PatchMapping, @DeleteMapping with explicit 'consumes' parameter.Validates that incoming requests have the expected Content-Type (application/json).Automatically rejects requests with invalid/missing Content-Type with HTTP 415.</t>
+  </si>
+  <si>
     <t>13.2.6</t>
   </si>
   <si>
@@ -2379,12 +2608,18 @@
     <t>Verify that if application assets, such as JavaScript libraries, CSS stylesheets or web fonts, are hosted externally on a content delivery network (CDN) or external provider, Subresource Integrity (SRI) is used to validate the integrity of the asset.</t>
   </si>
   <si>
+    <t>Is just a backend API</t>
+  </si>
+  <si>
     <t>14.2.4</t>
   </si>
   <si>
     <t>Verify that third party components come from pre-defined, trusted and continually maintained repositories. ([C2](https://owasp.org/www-project-proactive-controls/#div-numbering))</t>
   </si>
   <si>
+    <t>The use of maven helps ensure this</t>
+  </si>
+  <si>
     <t>14.2.5</t>
   </si>
   <si>
@@ -2412,6 +2647,9 @@
     <t>Verify that web or application server and application framework debug modes are disabled in production to eliminate debug features, developer consoles, and unintended security disclosures.</t>
   </si>
   <si>
+    <t>between lines 73 to 79</t>
+  </si>
+  <si>
     <t>14.3.3</t>
   </si>
   <si>
@@ -2427,42 +2665,66 @@
     <t>Verify that every HTTP response contains a Content-Type header. Also specify a safe character set (e.g., UTF-8, ISO-8859-1) if the content types are text/*, /+xml and application/xml. Content must match with the provided Content-Type header.</t>
   </si>
   <si>
+    <t>https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/devicemanagement/api/DeviceController.java</t>
+  </si>
+  <si>
+    <t>In the line75</t>
+  </si>
+  <si>
     <t>14.4.2</t>
   </si>
   <si>
     <t>Verify that all API responses contain Content-Disposition: attachment; filename="api.json" header (or other appropriate filename for the content type).</t>
   </si>
   <si>
+    <t>between line 146 to 149</t>
+  </si>
+  <si>
     <t>14.4.3</t>
   </si>
   <si>
     <t>Verify that a Content Security Policy (CSP) response header is in place that helps mitigate impact for XSS attacks like HTML, DOM, JSON, and JavaScript injection vulnerabilities.</t>
   </si>
   <si>
+    <t>between Lines 184-188</t>
+  </si>
+  <si>
     <t>14.4.4</t>
   </si>
   <si>
     <t>Verify that all responses contain a X-Content-Type-Options: nosniff header.</t>
   </si>
   <si>
+    <t>between Lines 184-188. By default nosniff is enabled</t>
+  </si>
+  <si>
     <t>14.4.5</t>
   </si>
   <si>
     <t>Verify that a Strict-Transport-Security header is included on all responses and for all subdomains, such as Strict-Transport-Security: max-age=15724800; includeSubdomains.</t>
   </si>
   <si>
+    <t>between line 99 to 100</t>
+  </si>
+  <si>
     <t>14.4.6</t>
   </si>
   <si>
     <t>Verify that a suitable Referrer-Policy header is included to avoid exposing sensitive information in the URL through the Referer header to untrusted parties.</t>
   </si>
   <si>
+    <t>between line 189 to 190</t>
+  </si>
+  <si>
     <t>14.4.7</t>
   </si>
   <si>
     <t>Verify that the content of a web application cannot be embedded in a third-party site by default and that embedding of the exact resources is only allowed where necessary by using suitable Content-Security-Policy: frame-ancestors and X-Frame-Options response headers.</t>
   </si>
   <si>
+    <t>between line 184 to 188</t>
+  </si>
+  <si>
     <t>HTTP Request Header Validation</t>
   </si>
   <si>
@@ -2472,12 +2734,18 @@
     <t>Verify that the application server only accepts the HTTP methods in use by the application/API, including pre-flight OPTIONS, and logs/alerts on any requests that are not valid for the application context.</t>
   </si>
   <si>
+    <t>between line 238 and 248</t>
+  </si>
+  <si>
     <t>14.5.2</t>
   </si>
   <si>
     <t>Verify that the supplied Origin header is not used for authentication or access control decisions, as the Origin header can easily be changed by an attacker.</t>
   </si>
   <si>
+    <t>Betweetn Line 220 and 227 .Because the validation is made by token the solution is compliant</t>
+  </si>
+  <si>
     <t>14.5.3</t>
   </si>
   <si>
@@ -2488,6 +2756,9 @@
   </si>
   <si>
     <t>Verify that HTTP headers added by a trusted proxy or SSO devices, such as a bearer token, are authenticated by the application.</t>
+  </si>
+  <si>
+    <t>Between Line 214 to 216</t>
   </si>
 </sst>
 </file>
@@ -2497,7 +2768,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00,_€;\-#,##0.00,_€"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2616,7 +2887,47 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF486581"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF486581"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF102A43"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2669,7 +2980,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -3287,19 +3598,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF243B53"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF243B53"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF243B53"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3634,9 +3965,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3647,10 +3976,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3920,46 +4282,46 @@
                   <c:v>89.65517241379311</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>57.142857142857139</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.82352941176471</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>92.307692307692307</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55.555555555555557</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>75</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>83.333333333333343</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>71.428571428571431</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>47.701149425287355</c:v>
+                  <c:v>97.31543624161074</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4170,6 +4532,55 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2400300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF8B9967-659D-A2DF-2060-881DC6489871}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12515850" y="7267575"/>
+          <a:ext cx="4572000" cy="2295525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4540,7 +4951,7 @@
     <col min="6" max="1024" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="42">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4581,15 +4992,15 @@
       </c>
       <c r="B3" s="9">
         <f>COUNTIF(Authentication!G2:G58,"Valid")</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIF(Authentication!G2:G58,"&lt;&gt;Not Applicable")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>57.142857142857139</v>
+        <v>100</v>
       </c>
       <c r="E3" s="12"/>
     </row>
@@ -4599,15 +5010,15 @@
       </c>
       <c r="B4" s="9">
         <f>COUNTIF('Session Management'!G2:G21,"Valid")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4" s="10">
         <f>COUNTIF('Session Management'!G2:G21,"&lt;&gt;Not Applicable")</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D4" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4" s="12"/>
     </row>
@@ -4635,15 +5046,15 @@
       </c>
       <c r="B6" s="9">
         <f>COUNTIF('Validation, Sanitization and En'!G2:G31,"Valid")</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C6" s="10">
         <f>COUNTIF('Validation, Sanitization and En'!G2:G31,"&lt;&gt;Not Applicable")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="11">
         <f t="shared" si="0"/>
-        <v>58.82352941176471</v>
+        <v>100</v>
       </c>
       <c r="E6" s="12"/>
     </row>
@@ -4653,15 +5064,15 @@
       </c>
       <c r="B7" s="9">
         <f>COUNTIF('Stored Cryptography'!G2:G17,"Valid")</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C7" s="10">
         <f>COUNTIF('Stored Cryptography'!G2:G17,"&lt;&gt;Not Applicable")</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>92.307692307692307</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="14"/>
@@ -4690,15 +5101,15 @@
       </c>
       <c r="B9" s="9">
         <f>COUNTIF('Data Protection'!G2:G18,"Valid")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" s="10">
         <f>COUNTIF('Data Protection'!G2:G18,"&lt;&gt;Not Applicable")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="11">
         <f t="shared" si="0"/>
-        <v>55.555555555555557</v>
+        <v>100</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -4726,7 +5137,7 @@
       </c>
       <c r="B11" s="9">
         <f>COUNTIF('Malicious Code'!G2:G11,"Valid")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="10">
         <f>COUNTIF('Malicious Code'!G2:G11,"&lt;&gt;Not Applicable")</f>
@@ -4734,7 +5145,7 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E11" s="12"/>
     </row>
@@ -4744,7 +5155,7 @@
       </c>
       <c r="B12" s="9">
         <f>COUNTIF('Business Logic'!G2:G9,"Valid")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="10">
         <f>COUNTIF('Business Logic'!G2:G9,"&lt;&gt;Not Applicable")</f>
@@ -4752,7 +5163,7 @@
       </c>
       <c r="D12" s="11">
         <f t="shared" si="0"/>
-        <v>83.333333333333343</v>
+        <v>100</v>
       </c>
       <c r="E12" s="12"/>
     </row>
@@ -4762,15 +5173,15 @@
       </c>
       <c r="B13" s="9">
         <f>COUNTIF('Files and Resources'!G2:G16,"Valid")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C13" s="10">
         <f>COUNTIF('Files and Resources'!G2:G16,"&lt;&gt;Not Applicable")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13" s="12"/>
     </row>
@@ -4780,7 +5191,7 @@
       </c>
       <c r="B14" s="9">
         <f>COUNTIF('API and Web Service'!G2:G16,"Valid")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="10">
         <f>COUNTIF('API and Web Service'!G2:G16,"&lt;&gt;Not Applicable")</f>
@@ -4788,7 +5199,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>71.428571428571431</v>
+        <v>100</v>
       </c>
       <c r="E14" s="12"/>
     </row>
@@ -4798,15 +5209,15 @@
       </c>
       <c r="B15" s="9">
         <f>COUNTIF(Configuration!G2:G26,"Valid")</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C15" s="10">
         <f>COUNTIF(Configuration!G2:G26,"&lt;&gt;Not Applicable")</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="12"/>
     </row>
@@ -4816,15 +5227,15 @@
       </c>
       <c r="B16" s="9">
         <f>SUM(B2:B15)</f>
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(C2:C15)</f>
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>47.701149425287355</v>
+        <v>97.31543624161074</v>
       </c>
       <c r="E16" s="12"/>
     </row>
@@ -4888,11 +5299,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1" thickBot="1">
-      <c r="A2" s="142" t="s">
-        <v>597</v>
+      <c r="A2" s="158" t="s">
+        <v>642</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>598</v>
+        <v>643</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -4902,23 +5313,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>599</v>
+        <v>644</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="130" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I2" s="49" t="s">
-        <v>601</v>
+        <v>646</v>
       </c>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="31.9" thickBot="1">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -4928,23 +5339,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>603</v>
+        <v>648</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="124" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I3" s="131" t="s">
-        <v>604</v>
+        <v>649</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="31.9" thickBot="1">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>605</v>
+        <v>650</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -4954,25 +5365,25 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="124" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>607</v>
+        <v>652</v>
       </c>
       <c r="J4" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="63.75" customHeight="1" thickBot="1">
-      <c r="A5" s="142" t="s">
-        <v>608</v>
+      <c r="A5" s="158" t="s">
+        <v>653</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>609</v>
+        <v>654</v>
       </c>
       <c r="C5" s="68">
         <v>2</v>
@@ -4982,23 +5393,23 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>610</v>
+        <v>655</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="124" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="63" thickBot="1">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="63.75" thickBot="1">
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>612</v>
+        <v>657</v>
       </c>
       <c r="C6" s="68">
         <v>2</v>
@@ -5008,23 +5419,23 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>613</v>
+        <v>658</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="124" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="31.9" thickBot="1">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>614</v>
+        <v>659</v>
       </c>
       <c r="C7" s="68">
         <v>2</v>
@@ -5034,7 +5445,7 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
@@ -5043,10 +5454,10 @@
       <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="31.9" thickBot="1">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>616</v>
+        <v>661</v>
       </c>
       <c r="C8" s="68">
         <v>2</v>
@@ -5056,7 +5467,7 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>617</v>
+        <v>662</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>75</v>
@@ -5065,10 +5476,10 @@
       <c r="I8" s="28"/>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="16.149999999999999" thickBot="1">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="16.5" thickBot="1">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>618</v>
+        <v>663</v>
       </c>
       <c r="C9" s="95">
         <v>3</v>
@@ -5078,16 +5489,16 @@
       </c>
       <c r="E9" s="71"/>
       <c r="F9" s="81" t="s">
-        <v>619</v>
+        <v>664</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>620</v>
+        <v>665</v>
       </c>
       <c r="J9" s="37"/>
     </row>
@@ -5166,12 +5577,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="31.15">
-      <c r="A2" s="1" t="s">
-        <v>621</v>
+    <row r="2" spans="1:10" ht="31.5">
+      <c r="A2" s="2" t="s">
+        <v>666</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>622</v>
+        <v>667</v>
       </c>
       <c r="C2" s="97">
         <v>3</v>
@@ -5181,25 +5592,25 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>624</v>
+        <v>669</v>
       </c>
       <c r="I2" s="49" t="s">
-        <v>625</v>
+        <v>670</v>
       </c>
       <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="48" customHeight="1">
-      <c r="A3" s="142" t="s">
-        <v>626</v>
+      <c r="A3" s="158" t="s">
+        <v>671</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>627</v>
+        <v>672</v>
       </c>
       <c r="C3" s="68">
         <v>2</v>
@@ -5209,23 +5620,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>628</v>
+        <v>673</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="124" t="s">
-        <v>629</v>
+        <v>674</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>630</v>
+        <v>675</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="31.15">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="31.5">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>631</v>
+        <v>676</v>
       </c>
       <c r="C4" s="68">
         <v>2</v>
@@ -5235,7 +5646,7 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>632</v>
+        <v>677</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>75</v>
@@ -5244,10 +5655,10 @@
       <c r="I4" s="28"/>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="78">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="78.75">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>633</v>
+        <v>678</v>
       </c>
       <c r="C5" s="69">
         <v>3</v>
@@ -5257,7 +5668,7 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>634</v>
+        <v>679</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>75</v>
@@ -5266,10 +5677,10 @@
       <c r="I5" s="28"/>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="31.15">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="31.5">
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>635</v>
+        <v>680</v>
       </c>
       <c r="C6" s="69">
         <v>3</v>
@@ -5279,7 +5690,7 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>75</v>
@@ -5288,10 +5699,10 @@
       <c r="I6" s="28"/>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="31.15">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="31.5">
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="C7" s="69">
         <v>3</v>
@@ -5301,7 +5712,7 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
@@ -5310,10 +5721,10 @@
       <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="31.15">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="31.5">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="C8" s="69">
         <v>3</v>
@@ -5323,7 +5734,7 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>75</v>
@@ -5333,11 +5744,11 @@
       <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10" ht="48" customHeight="1">
-      <c r="A9" s="142" t="s">
-        <v>641</v>
+      <c r="A9" s="158" t="s">
+        <v>686</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>642</v>
+        <v>687</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -5347,7 +5758,7 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
@@ -5356,10 +5767,10 @@
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="48.75">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="63">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>644</v>
+        <v>689</v>
       </c>
       <c r="C10" s="66">
         <v>1</v>
@@ -5369,19 +5780,23 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H10" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="141" t="s">
+        <v>691</v>
+      </c>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="96.75">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="94.5">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>646</v>
+        <v>692</v>
       </c>
       <c r="C11" s="70">
         <v>1</v>
@@ -5391,16 +5806,16 @@
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="81" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="136" t="s">
-        <v>648</v>
-      </c>
-      <c r="I11" s="137" t="s">
-        <v>649</v>
+      <c r="H11" s="134" t="s">
+        <v>694</v>
+      </c>
+      <c r="I11" s="149" t="s">
+        <v>695</v>
       </c>
       <c r="J11" s="37"/>
     </row>
@@ -5477,11 +5892,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>650</v>
+      <c r="A2" s="158" t="s">
+        <v>696</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -5491,19 +5906,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+        <v>26</v>
+      </c>
+      <c r="H2" s="146" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="143" t="s">
+        <v>699</v>
+      </c>
       <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="142.5" customHeight="1">
-      <c r="A3" s="142"/>
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -5513,23 +5932,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>654</v>
+        <v>701</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="124" t="s">
-        <v>655</v>
-      </c>
-      <c r="I3" s="140" t="s">
-        <v>656</v>
+        <v>702</v>
+      </c>
+      <c r="I3" s="138" t="s">
+        <v>703</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="32.25">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="31.5">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -5539,23 +5958,23 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>658</v>
+        <v>705</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="124" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="48.75">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="C5" s="66">
         <v>1</v>
@@ -5565,23 +5984,23 @@
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="80" t="s">
-        <v>661</v>
+        <v>708</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="124" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="J5" s="32"/>
     </row>
     <row r="6" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A6" s="142"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>662</v>
+        <v>709</v>
       </c>
       <c r="C6" s="66">
         <v>1</v>
@@ -5591,23 +6010,23 @@
       </c>
       <c r="E6" s="27"/>
       <c r="F6" s="80" t="s">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="124" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10" ht="121.5" customHeight="1">
-      <c r="A7" s="142"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>664</v>
+        <v>711</v>
       </c>
       <c r="C7" s="68">
         <v>2</v>
@@ -5617,23 +6036,23 @@
       </c>
       <c r="E7" s="27"/>
       <c r="F7" s="80" t="s">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>666</v>
-      </c>
-      <c r="I7" s="139" t="s">
-        <v>667</v>
+        <v>713</v>
+      </c>
+      <c r="I7" s="137" t="s">
+        <v>714</v>
       </c>
       <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10" ht="66.75" customHeight="1">
-      <c r="A8" s="142"/>
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="C8" s="68">
         <v>2</v>
@@ -5643,19 +6062,19 @@
       </c>
       <c r="E8" s="27"/>
       <c r="F8" s="80" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H8" s="28"/>
-      <c r="I8" s="138"/>
+      <c r="I8" s="136"/>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="32.25">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="31.5">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>670</v>
+        <v>717</v>
       </c>
       <c r="C9" s="78">
         <v>2</v>
@@ -5665,7 +6084,7 @@
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="81" t="s">
-        <v>671</v>
+        <v>718</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>75</v>
@@ -5716,7 +6135,7 @@
     <col min="11" max="1024" width="8.7109375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="43" customFormat="1" ht="42">
+    <row r="1" spans="1:10" s="43" customFormat="1" ht="42.75" thickBot="1">
       <c r="A1" s="94" t="s">
         <v>20</v>
       </c>
@@ -5748,12 +6167,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>672</v>
+    <row r="2" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A2" s="158" t="s">
+        <v>719</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>673</v>
+        <v>720</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -5763,19 +6182,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>674</v>
+        <v>721</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+        <v>26</v>
+      </c>
+      <c r="H2" s="135" t="s">
+        <v>645</v>
+      </c>
+      <c r="I2" s="143" t="s">
+        <v>722</v>
+      </c>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="46.9">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="48" thickBot="1">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>675</v>
+        <v>723</v>
       </c>
       <c r="C3" s="68">
         <v>2</v>
@@ -5785,19 +6208,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>676</v>
+        <v>724</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+        <v>75</v>
+      </c>
+      <c r="H3" s="124" t="s">
+        <v>725</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>726</v>
+      </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="46.9">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="46.5" customHeight="1">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>677</v>
+        <v>727</v>
       </c>
       <c r="C4" s="68">
         <v>2</v>
@@ -5807,23 +6234,25 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>678</v>
+        <v>728</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H4" s="124" t="s">
+        <v>645</v>
+      </c>
       <c r="I4" s="28" t="s">
-        <v>679</v>
+        <v>729</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="31.15">
-      <c r="A5" s="1" t="s">
-        <v>680</v>
+    <row r="5" spans="1:10" ht="31.5">
+      <c r="A5" s="2" t="s">
+        <v>730</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>681</v>
+        <v>731</v>
       </c>
       <c r="C5" s="68">
         <v>2</v>
@@ -5833,21 +6262,25 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>682</v>
+        <v>732</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H5" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>733</v>
+      </c>
       <c r="J5" s="32"/>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1">
-      <c r="A6" s="142" t="s">
-        <v>683</v>
+      <c r="A6" s="158" t="s">
+        <v>734</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>684</v>
+        <v>735</v>
       </c>
       <c r="C6" s="66">
         <v>1</v>
@@ -5857,19 +6290,23 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>685</v>
+        <v>736</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H6" s="124" t="s">
+        <v>737</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>738</v>
+      </c>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="31.15">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="31.5">
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>686</v>
+        <v>739</v>
       </c>
       <c r="C7" s="66">
         <v>1</v>
@@ -5879,7 +6316,7 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>687</v>
+        <v>740</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
@@ -5888,10 +6325,10 @@
       <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="46.9">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="47.25">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>688</v>
+        <v>741</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -5901,7 +6338,7 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>689</v>
+        <v>742</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>75</v>
@@ -5910,10 +6347,10 @@
       <c r="I8" s="28"/>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="62.45">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="63">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>690</v>
+        <v>743</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -5923,7 +6360,7 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>691</v>
+        <v>744</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
@@ -5932,10 +6369,10 @@
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="31.15">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="31.5">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>692</v>
+        <v>745</v>
       </c>
       <c r="C10" s="66">
         <v>1</v>
@@ -5945,7 +6382,7 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>693</v>
+        <v>746</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>75</v>
@@ -5954,10 +6391,10 @@
       <c r="I10" s="28"/>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="46.9">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="47.25">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>694</v>
+        <v>747</v>
       </c>
       <c r="C11" s="68">
         <v>2</v>
@@ -5967,7 +6404,7 @@
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="80" t="s">
-        <v>695</v>
+        <v>748</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>75</v>
@@ -5977,11 +6414,11 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A12" s="142" t="s">
-        <v>696</v>
+      <c r="A12" s="158" t="s">
+        <v>749</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>697</v>
+        <v>750</v>
       </c>
       <c r="C12" s="66">
         <v>1</v>
@@ -5991,19 +6428,23 @@
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="80" t="s">
-        <v>698</v>
+        <v>751</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H12" s="124" t="s">
+        <v>752</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>753</v>
+      </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="31.15">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" ht="31.5">
+      <c r="A13" s="158"/>
       <c r="B13" s="62" t="s">
-        <v>699</v>
+        <v>754</v>
       </c>
       <c r="C13" s="66">
         <v>1</v>
@@ -6013,21 +6454,21 @@
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="80" t="s">
-        <v>700</v>
+        <v>755</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H13" s="28"/>
       <c r="I13" s="28"/>
       <c r="J13" s="32"/>
     </row>
     <row r="14" spans="1:10" ht="79.5" customHeight="1">
-      <c r="A14" s="142" t="s">
-        <v>701</v>
+      <c r="A14" s="158" t="s">
+        <v>756</v>
       </c>
       <c r="B14" s="62" t="s">
-        <v>702</v>
+        <v>757</v>
       </c>
       <c r="C14" s="66">
         <v>1</v>
@@ -6037,7 +6478,7 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="80" t="s">
-        <v>703</v>
+        <v>758</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>75</v>
@@ -6046,10 +6487,10 @@
       <c r="I14" s="28"/>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" ht="31.15">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" ht="31.5">
+      <c r="A15" s="158"/>
       <c r="B15" s="62" t="s">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="C15" s="66">
         <v>1</v>
@@ -6059,7 +6500,7 @@
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="80" t="s">
-        <v>705</v>
+        <v>760</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>75</v>
@@ -6068,12 +6509,12 @@
       <c r="I15" s="28"/>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" ht="46.9">
-      <c r="A16" s="1" t="s">
-        <v>706</v>
+    <row r="16" spans="1:10" ht="47.25">
+      <c r="A16" s="2" t="s">
+        <v>761</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>707</v>
+        <v>762</v>
       </c>
       <c r="C16" s="70">
         <v>1</v>
@@ -6083,7 +6524,7 @@
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="81" t="s">
-        <v>708</v>
+        <v>763</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>75</v>
@@ -6105,6 +6546,13 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H12" r:id="rId1" xr:uid="{BB6226E6-6240-4B1A-A38B-1CB2633AEB48}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{36BD1D48-15D9-4ED1-8C44-69CBD48DB279}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{1806666E-7CA5-4323-9F07-D402D0F42C57}"/>
+    <hyperlink ref="H4" r:id="rId4" xr:uid="{2C686002-6763-4138-AE73-1511FAE3DD61}"/>
+    <hyperlink ref="H6" r:id="rId5" location="L87" xr:uid="{73EC1003-B571-455C-B3FC-89B80A9351CD}"/>
+  </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -6162,11 +6610,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>709</v>
+      <c r="A2" s="158" t="s">
+        <v>764</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>710</v>
+        <v>765</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -6176,19 +6624,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>711</v>
+        <v>766</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+        <v>26</v>
+      </c>
+      <c r="H2" s="130" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="150" t="s">
+        <v>767</v>
+      </c>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="15.6">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="15.75">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>712</v>
+        <v>768</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -6198,7 +6650,7 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>75</v>
@@ -6208,9 +6660,9 @@
       <c r="J3" s="32"/>
     </row>
     <row r="4" spans="1:10" ht="35.25" customHeight="1">
-      <c r="A4" s="142"/>
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -6220,23 +6672,23 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>715</v>
+        <v>771</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="124" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="48.75">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="C5" s="68">
         <v>2</v>
@@ -6246,23 +6698,23 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="135" t="s">
+      <c r="H5" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="J5" s="32"/>
     </row>
     <row r="6" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A6" s="142"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>720</v>
+        <v>776</v>
       </c>
       <c r="C6" s="68">
         <v>2</v>
@@ -6272,7 +6724,7 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>75</v>
@@ -6282,11 +6734,11 @@
       <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A7" s="142" t="s">
-        <v>722</v>
+      <c r="A7" s="158" t="s">
+        <v>778</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>723</v>
+        <v>779</v>
       </c>
       <c r="C7" s="66">
         <v>1</v>
@@ -6296,23 +6748,23 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>724</v>
+        <v>780</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="135" t="s">
+      <c r="H7" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="16.5">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="15.75">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>725</v>
+        <v>781</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -6322,23 +6774,23 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>726</v>
+        <v>782</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="135" t="s">
-        <v>417</v>
+      <c r="H8" s="124" t="s">
+        <v>440</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>727</v>
+        <v>783</v>
       </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="46.9">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="47.25">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>728</v>
+        <v>784</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -6348,7 +6800,7 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>729</v>
+        <v>785</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
@@ -6357,10 +6809,10 @@
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="15.6">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="15.75">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>730</v>
+        <v>786</v>
       </c>
       <c r="C10" s="68">
         <v>2</v>
@@ -6370,7 +6822,7 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>75</v>
@@ -6379,10 +6831,10 @@
       <c r="I10" s="28"/>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="32.25">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="31.5">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>732</v>
+        <v>788</v>
       </c>
       <c r="C11" s="68">
         <v>2</v>
@@ -6392,19 +6844,23 @@
       </c>
       <c r="E11" s="67"/>
       <c r="F11" s="80" t="s">
-        <v>733</v>
+        <v>789</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H11" s="124" t="s">
+        <v>268</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>790</v>
+      </c>
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A12" s="142"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="62" t="s">
-        <v>734</v>
+        <v>791</v>
       </c>
       <c r="C12" s="68">
         <v>2</v>
@@ -6414,25 +6870,25 @@
       </c>
       <c r="E12" s="67"/>
       <c r="F12" s="80" t="s">
-        <v>735</v>
+        <v>792</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="124" t="s">
-        <v>600</v>
+        <v>645</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>611</v>
+        <v>656</v>
       </c>
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:10" ht="48" customHeight="1">
-      <c r="A13" s="142" t="s">
-        <v>736</v>
+      <c r="A13" s="158" t="s">
+        <v>793</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>737</v>
+        <v>794</v>
       </c>
       <c r="C13" s="66">
         <v>1</v>
@@ -6442,7 +6898,7 @@
       </c>
       <c r="E13" s="67"/>
       <c r="F13" s="80" t="s">
-        <v>738</v>
+        <v>795</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>75</v>
@@ -6451,10 +6907,10 @@
       <c r="I13" s="28"/>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="31.15">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="31.5">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>739</v>
+        <v>796</v>
       </c>
       <c r="C14" s="68">
         <v>2</v>
@@ -6464,7 +6920,7 @@
       </c>
       <c r="E14" s="67"/>
       <c r="F14" s="80" t="s">
-        <v>740</v>
+        <v>797</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>75</v>
@@ -6474,11 +6930,11 @@
       <c r="J14" s="32"/>
     </row>
     <row r="15" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A15" s="142" t="s">
-        <v>741</v>
+      <c r="A15" s="158" t="s">
+        <v>798</v>
       </c>
       <c r="B15" s="62" t="s">
-        <v>742</v>
+        <v>799</v>
       </c>
       <c r="C15" s="68">
         <v>2</v>
@@ -6488,7 +6944,7 @@
       </c>
       <c r="E15" s="67"/>
       <c r="F15" s="80" t="s">
-        <v>743</v>
+        <v>800</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>75</v>
@@ -6497,10 +6953,10 @@
       <c r="I15" s="28"/>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" ht="31.15">
-      <c r="A16" s="142"/>
+    <row r="16" spans="1:10" ht="31.5">
+      <c r="A16" s="158"/>
       <c r="B16" s="62" t="s">
-        <v>744</v>
+        <v>801</v>
       </c>
       <c r="C16" s="78">
         <v>2</v>
@@ -6510,7 +6966,7 @@
       </c>
       <c r="E16" s="71"/>
       <c r="F16" s="81" t="s">
-        <v>745</v>
+        <v>802</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>75</v>
@@ -6538,6 +6994,8 @@
     <hyperlink ref="H5" r:id="rId3" xr:uid="{F825BF48-171F-4F29-B479-A8F25DAE012C}"/>
     <hyperlink ref="H7" r:id="rId4" xr:uid="{CFCE09E8-9D9A-417A-94CF-EE56BDCA3496}"/>
     <hyperlink ref="H8" r:id="rId5" xr:uid="{5F804BF8-D99E-4E33-BF26-57C6D8988C0A}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{8A7002FB-0755-EE40-BAFD-39C900E62404}"/>
+    <hyperlink ref="H2" r:id="rId7" xr:uid="{2A766E73-53A3-1649-9931-3F85DC96C4F5}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6558,7 +7016,7 @@
     <col min="3" max="5" width="8.7109375" style="25"/>
     <col min="6" max="6" width="88.7109375" style="25" customWidth="1"/>
     <col min="7" max="7" width="17.140625" style="25" customWidth="1"/>
-    <col min="8" max="8" width="35.28515625" style="25" customWidth="1"/>
+    <col min="8" max="8" width="69.140625" style="25" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" style="25" customWidth="1"/>
     <col min="10" max="10" width="33.42578125" style="25" customWidth="1"/>
     <col min="11" max="1024" width="8.7109375" style="25"/>
@@ -6597,11 +7055,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="143" t="s">
-        <v>746</v>
+      <c r="A2" s="162" t="s">
+        <v>803</v>
       </c>
       <c r="B2" s="99" t="s">
-        <v>747</v>
+        <v>804</v>
       </c>
       <c r="C2" s="100">
         <v>2</v>
@@ -6609,17 +7067,21 @@
       <c r="D2" s="101"/>
       <c r="E2" s="102"/>
       <c r="F2" s="103" t="s">
-        <v>748</v>
-      </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
+        <v>805</v>
+      </c>
+      <c r="G2" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="139" t="s">
+        <v>560</v>
+      </c>
       <c r="I2" s="104"/>
       <c r="J2" s="105"/>
     </row>
-    <row r="3" spans="1:10" ht="46.9">
-      <c r="A3" s="143"/>
+    <row r="3" spans="1:10" ht="47.25">
+      <c r="A3" s="162"/>
       <c r="B3" s="62" t="s">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="C3" s="106">
         <v>2</v>
@@ -6629,17 +7091,19 @@
       </c>
       <c r="E3" s="108"/>
       <c r="F3" s="109" t="s">
-        <v>750</v>
-      </c>
-      <c r="G3" s="110"/>
+        <v>807</v>
+      </c>
+      <c r="G3" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H3" s="110"/>
       <c r="I3" s="110"/>
       <c r="J3" s="111"/>
     </row>
-    <row r="4" spans="1:10" ht="31.15">
-      <c r="A4" s="143"/>
+    <row r="4" spans="1:10" ht="31.5">
+      <c r="A4" s="162"/>
       <c r="B4" s="62" t="s">
-        <v>751</v>
+        <v>808</v>
       </c>
       <c r="C4" s="106">
         <v>2</v>
@@ -6649,17 +7113,19 @@
       </c>
       <c r="E4" s="108"/>
       <c r="F4" s="109" t="s">
-        <v>752</v>
-      </c>
-      <c r="G4" s="110"/>
+        <v>809</v>
+      </c>
+      <c r="G4" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H4" s="110"/>
       <c r="I4" s="110"/>
       <c r="J4" s="111"/>
     </row>
-    <row r="5" spans="1:10" ht="46.9">
-      <c r="A5" s="143"/>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="162"/>
       <c r="B5" s="62" t="s">
-        <v>753</v>
+        <v>810</v>
       </c>
       <c r="C5" s="106">
         <v>2</v>
@@ -6667,17 +7133,19 @@
       <c r="D5" s="107"/>
       <c r="E5" s="108"/>
       <c r="F5" s="109" t="s">
-        <v>754</v>
-      </c>
-      <c r="G5" s="110"/>
+        <v>811</v>
+      </c>
+      <c r="G5" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H5" s="110"/>
       <c r="I5" s="110"/>
       <c r="J5" s="111"/>
     </row>
-    <row r="6" spans="1:10" ht="31.15">
-      <c r="A6" s="143"/>
+    <row r="6" spans="1:10" ht="31.5">
+      <c r="A6" s="162"/>
       <c r="B6" s="62" t="s">
-        <v>755</v>
+        <v>812</v>
       </c>
       <c r="C6" s="112">
         <v>3</v>
@@ -6685,19 +7153,21 @@
       <c r="D6" s="107"/>
       <c r="E6" s="108"/>
       <c r="F6" s="109" t="s">
-        <v>756</v>
-      </c>
-      <c r="G6" s="110"/>
+        <v>813</v>
+      </c>
+      <c r="G6" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H6" s="110"/>
       <c r="I6" s="110"/>
       <c r="J6" s="111"/>
     </row>
     <row r="7" spans="1:10" ht="48" customHeight="1">
-      <c r="A7" s="142" t="s">
-        <v>757</v>
+      <c r="A7" s="158" t="s">
+        <v>814</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>758</v>
+        <v>815</v>
       </c>
       <c r="C7" s="113">
         <v>1</v>
@@ -6707,17 +7177,21 @@
       </c>
       <c r="E7" s="108"/>
       <c r="F7" s="109" t="s">
-        <v>759</v>
-      </c>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
+        <v>816</v>
+      </c>
+      <c r="G7" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="144" t="s">
+        <v>674</v>
+      </c>
       <c r="I7" s="110"/>
       <c r="J7" s="111"/>
     </row>
-    <row r="8" spans="1:10" ht="31.15">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="31.5">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>760</v>
+        <v>817</v>
       </c>
       <c r="C8" s="113">
         <v>1</v>
@@ -6727,17 +7201,19 @@
       </c>
       <c r="E8" s="108"/>
       <c r="F8" s="109" t="s">
-        <v>761</v>
-      </c>
-      <c r="G8" s="110"/>
+        <v>818</v>
+      </c>
+      <c r="G8" s="110" t="s">
+        <v>26</v>
+      </c>
       <c r="H8" s="110"/>
       <c r="I8" s="110"/>
       <c r="J8" s="111"/>
     </row>
-    <row r="9" spans="1:10" ht="46.9">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="47.25">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>762</v>
+        <v>819</v>
       </c>
       <c r="C9" s="113">
         <v>1</v>
@@ -6747,17 +7223,21 @@
       </c>
       <c r="E9" s="108"/>
       <c r="F9" s="109" t="s">
-        <v>763</v>
-      </c>
-      <c r="G9" s="110"/>
+        <v>820</v>
+      </c>
+      <c r="G9" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
+      <c r="I9" s="110" t="s">
+        <v>821</v>
+      </c>
       <c r="J9" s="111"/>
     </row>
-    <row r="10" spans="1:10" ht="46.9">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="47.25">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>764</v>
+        <v>822</v>
       </c>
       <c r="C10" s="106">
         <v>2</v>
@@ -6767,17 +7247,23 @@
       </c>
       <c r="E10" s="108"/>
       <c r="F10" s="109" t="s">
-        <v>765</v>
-      </c>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
+        <v>823</v>
+      </c>
+      <c r="G10" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="144" t="s">
+        <v>674</v>
+      </c>
+      <c r="I10" s="110" t="s">
+        <v>824</v>
+      </c>
       <c r="J10" s="111"/>
     </row>
-    <row r="11" spans="1:10" ht="31.15">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="31.5">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>766</v>
+        <v>825</v>
       </c>
       <c r="C11" s="106">
         <v>2</v>
@@ -6785,17 +7271,19 @@
       <c r="D11" s="107"/>
       <c r="E11" s="108"/>
       <c r="F11" s="109" t="s">
-        <v>767</v>
-      </c>
-      <c r="G11" s="110"/>
+        <v>826</v>
+      </c>
+      <c r="G11" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H11" s="110"/>
       <c r="I11" s="110"/>
       <c r="J11" s="111"/>
     </row>
-    <row r="12" spans="1:10" ht="46.9">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" ht="47.25">
+      <c r="A12" s="158"/>
       <c r="B12" s="62" t="s">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="C12" s="106">
         <v>2</v>
@@ -6805,19 +7293,21 @@
       </c>
       <c r="E12" s="108"/>
       <c r="F12" s="109" t="s">
-        <v>769</v>
-      </c>
-      <c r="G12" s="110"/>
+        <v>828</v>
+      </c>
+      <c r="G12" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H12" s="110"/>
       <c r="I12" s="110"/>
       <c r="J12" s="111"/>
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A13" s="142" t="s">
-        <v>770</v>
+      <c r="A13" s="158" t="s">
+        <v>829</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>771</v>
+        <v>830</v>
       </c>
       <c r="C13" s="113">
         <v>1</v>
@@ -6827,7 +7317,7 @@
       </c>
       <c r="E13" s="108"/>
       <c r="F13" s="109" t="s">
-        <v>772</v>
+        <v>831</v>
       </c>
       <c r="G13" s="110" t="s">
         <v>75</v>
@@ -6836,10 +7326,10 @@
       <c r="I13" s="110"/>
       <c r="J13" s="111"/>
     </row>
-    <row r="14" spans="1:10" ht="46.9">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="47.25">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>773</v>
+        <v>832</v>
       </c>
       <c r="C14" s="113">
         <v>1</v>
@@ -6849,17 +7339,23 @@
       </c>
       <c r="E14" s="108"/>
       <c r="F14" s="109" t="s">
-        <v>774</v>
-      </c>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
+        <v>833</v>
+      </c>
+      <c r="G14" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="152" t="s">
+        <v>645</v>
+      </c>
+      <c r="I14" s="110" t="s">
+        <v>834</v>
+      </c>
       <c r="J14" s="111"/>
     </row>
-    <row r="15" spans="1:10" ht="31.15">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" ht="193.5" customHeight="1">
+      <c r="A15" s="158"/>
       <c r="B15" s="62" t="s">
-        <v>775</v>
+        <v>835</v>
       </c>
       <c r="C15" s="113">
         <v>1</v>
@@ -6869,19 +7365,21 @@
       </c>
       <c r="E15" s="108"/>
       <c r="F15" s="109" t="s">
-        <v>776</v>
-      </c>
-      <c r="G15" s="110"/>
+        <v>836</v>
+      </c>
+      <c r="G15" s="110" t="s">
+        <v>26</v>
+      </c>
       <c r="H15" s="110"/>
       <c r="I15" s="110"/>
       <c r="J15" s="111"/>
     </row>
     <row r="16" spans="1:10" ht="48" customHeight="1">
-      <c r="A16" s="142" t="s">
-        <v>777</v>
+      <c r="A16" s="158" t="s">
+        <v>837</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>778</v>
+        <v>838</v>
       </c>
       <c r="C16" s="113">
         <v>1</v>
@@ -6891,17 +7389,23 @@
       </c>
       <c r="E16" s="108"/>
       <c r="F16" s="109" t="s">
-        <v>779</v>
-      </c>
-      <c r="G16" s="110"/>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
+        <v>839</v>
+      </c>
+      <c r="G16" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="152" t="s">
+        <v>840</v>
+      </c>
+      <c r="I16" s="110" t="s">
+        <v>841</v>
+      </c>
       <c r="J16" s="111"/>
     </row>
-    <row r="17" spans="1:10" ht="31.15">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" ht="31.5">
+      <c r="A17" s="158"/>
       <c r="B17" s="62" t="s">
-        <v>780</v>
+        <v>842</v>
       </c>
       <c r="C17" s="113">
         <v>1</v>
@@ -6911,17 +7415,23 @@
       </c>
       <c r="E17" s="108"/>
       <c r="F17" s="109" t="s">
-        <v>781</v>
-      </c>
-      <c r="G17" s="110"/>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
+        <v>843</v>
+      </c>
+      <c r="G17" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="152" t="s">
+        <v>840</v>
+      </c>
+      <c r="I17" s="110" t="s">
+        <v>844</v>
+      </c>
       <c r="J17" s="111"/>
     </row>
-    <row r="18" spans="1:10" ht="31.15">
-      <c r="A18" s="142"/>
+    <row r="18" spans="1:10" ht="31.5">
+      <c r="A18" s="158"/>
       <c r="B18" s="62" t="s">
-        <v>782</v>
+        <v>845</v>
       </c>
       <c r="C18" s="113">
         <v>1</v>
@@ -6931,17 +7441,23 @@
       </c>
       <c r="E18" s="108"/>
       <c r="F18" s="109" t="s">
-        <v>783</v>
-      </c>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
+        <v>846</v>
+      </c>
+      <c r="G18" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="110" t="s">
+        <v>847</v>
+      </c>
       <c r="J18" s="111"/>
     </row>
-    <row r="19" spans="1:10" ht="15.6">
-      <c r="A19" s="142"/>
+    <row r="19" spans="1:10" ht="15.75">
+      <c r="A19" s="158"/>
       <c r="B19" s="62" t="s">
-        <v>784</v>
+        <v>848</v>
       </c>
       <c r="C19" s="113">
         <v>1</v>
@@ -6951,17 +7467,23 @@
       </c>
       <c r="E19" s="108"/>
       <c r="F19" s="109" t="s">
-        <v>785</v>
-      </c>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
+        <v>849</v>
+      </c>
+      <c r="G19" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="110" t="s">
+        <v>850</v>
+      </c>
       <c r="J19" s="111"/>
     </row>
-    <row r="20" spans="1:10" ht="31.15">
-      <c r="A20" s="142"/>
+    <row r="20" spans="1:10" ht="31.5">
+      <c r="A20" s="158"/>
       <c r="B20" s="62" t="s">
-        <v>786</v>
+        <v>851</v>
       </c>
       <c r="C20" s="113">
         <v>1</v>
@@ -6971,17 +7493,23 @@
       </c>
       <c r="E20" s="108"/>
       <c r="F20" s="109" t="s">
-        <v>787</v>
-      </c>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
+        <v>852</v>
+      </c>
+      <c r="G20" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="110" t="s">
+        <v>853</v>
+      </c>
       <c r="J20" s="111"/>
     </row>
-    <row r="21" spans="1:10" ht="31.15">
-      <c r="A21" s="142"/>
+    <row r="21" spans="1:10" ht="31.5">
+      <c r="A21" s="158"/>
       <c r="B21" s="62" t="s">
-        <v>788</v>
+        <v>854</v>
       </c>
       <c r="C21" s="113">
         <v>1</v>
@@ -6991,17 +7519,23 @@
       </c>
       <c r="E21" s="108"/>
       <c r="F21" s="109" t="s">
-        <v>789</v>
-      </c>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
+        <v>855</v>
+      </c>
+      <c r="G21" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="110" t="s">
+        <v>856</v>
+      </c>
       <c r="J21" s="111"/>
     </row>
-    <row r="22" spans="1:10" ht="62.45">
-      <c r="A22" s="142"/>
+    <row r="22" spans="1:10" ht="47.25">
+      <c r="A22" s="158"/>
       <c r="B22" s="62" t="s">
-        <v>790</v>
+        <v>857</v>
       </c>
       <c r="C22" s="113">
         <v>1</v>
@@ -7011,19 +7545,25 @@
       </c>
       <c r="E22" s="108"/>
       <c r="F22" s="109" t="s">
-        <v>791</v>
-      </c>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
+        <v>858</v>
+      </c>
+      <c r="G22" s="145" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="144" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="110" t="s">
+        <v>859</v>
+      </c>
       <c r="J22" s="111"/>
     </row>
     <row r="23" spans="1:10" ht="48" customHeight="1">
-      <c r="A23" s="142" t="s">
-        <v>792</v>
+      <c r="A23" s="158" t="s">
+        <v>860</v>
       </c>
       <c r="B23" s="62" t="s">
-        <v>793</v>
+        <v>861</v>
       </c>
       <c r="C23" s="113">
         <v>1</v>
@@ -7033,17 +7573,23 @@
       </c>
       <c r="E23" s="108"/>
       <c r="F23" s="109" t="s">
-        <v>794</v>
-      </c>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
+        <v>862</v>
+      </c>
+      <c r="G23" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="110" t="s">
+        <v>863</v>
+      </c>
       <c r="J23" s="111"/>
     </row>
-    <row r="24" spans="1:10" ht="31.15">
-      <c r="A24" s="142"/>
+    <row r="24" spans="1:10" ht="31.5">
+      <c r="A24" s="158"/>
       <c r="B24" s="62" t="s">
-        <v>795</v>
+        <v>864</v>
       </c>
       <c r="C24" s="113">
         <v>1</v>
@@ -7053,17 +7599,23 @@
       </c>
       <c r="E24" s="108"/>
       <c r="F24" s="109" t="s">
-        <v>796</v>
-      </c>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
+        <v>865</v>
+      </c>
+      <c r="G24" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="110" t="s">
+        <v>866</v>
+      </c>
       <c r="J24" s="111"/>
     </row>
-    <row r="25" spans="1:10" ht="46.9">
-      <c r="A25" s="142"/>
+    <row r="25" spans="1:10" ht="47.25">
+      <c r="A25" s="158"/>
       <c r="B25" s="62" t="s">
-        <v>797</v>
+        <v>867</v>
       </c>
       <c r="C25" s="113">
         <v>1</v>
@@ -7073,17 +7625,19 @@
       </c>
       <c r="E25" s="108"/>
       <c r="F25" s="109" t="s">
-        <v>798</v>
-      </c>
-      <c r="G25" s="110"/>
+        <v>868</v>
+      </c>
+      <c r="G25" s="110" t="s">
+        <v>75</v>
+      </c>
       <c r="H25" s="110"/>
       <c r="I25" s="110"/>
       <c r="J25" s="111"/>
     </row>
-    <row r="26" spans="1:10" ht="31.15">
-      <c r="A26" s="142"/>
+    <row r="26" spans="1:10" ht="31.5">
+      <c r="A26" s="158"/>
       <c r="B26" s="62" t="s">
-        <v>799</v>
+        <v>869</v>
       </c>
       <c r="C26" s="114">
         <v>2</v>
@@ -7093,11 +7647,17 @@
       </c>
       <c r="E26" s="116"/>
       <c r="F26" s="117" t="s">
-        <v>800</v>
-      </c>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
+        <v>870</v>
+      </c>
+      <c r="G26" s="118" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="153" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" s="118" t="s">
+        <v>871</v>
+      </c>
       <c r="J26" s="119"/>
     </row>
   </sheetData>
@@ -7114,12 +7674,29 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{9081D9FA-C9DE-4D0F-A77D-77F483421BC2}"/>
+    <hyperlink ref="H10" r:id="rId2" xr:uid="{1F4A389E-E94B-4D80-A703-104BC314A612}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{D74D6A3D-C51B-4DCE-8F62-1BCF288E0E77}"/>
+    <hyperlink ref="H22" r:id="rId4" xr:uid="{B995F93D-62D1-4DAE-A94D-4911A49F7903}"/>
+    <hyperlink ref="H23" r:id="rId5" xr:uid="{DEDD469E-D26E-4C35-AE93-2F5CB783CCB0}"/>
+    <hyperlink ref="H24" r:id="rId6" xr:uid="{13DFB54C-FBA0-4684-869D-CCE31948CE32}"/>
+    <hyperlink ref="H26" r:id="rId7" xr:uid="{209B1627-E815-4910-BC66-911A40A3792F}"/>
+    <hyperlink ref="H16" r:id="rId8" xr:uid="{234BC9AF-041D-4449-B4F0-EB14F1D21B9D}"/>
+    <hyperlink ref="H17" r:id="rId9" xr:uid="{4FE65DBE-81F5-477D-8DD5-235E053C8466}"/>
+    <hyperlink ref="H18" r:id="rId10" xr:uid="{27F2A929-7B0E-407B-8938-FF6C109DD91E}"/>
+    <hyperlink ref="H19" r:id="rId11" xr:uid="{5E27B9CC-66F3-4F7D-A94C-E8074DAEED45}"/>
+    <hyperlink ref="H20" r:id="rId12" xr:uid="{9412BE25-BBBF-49B4-A223-FE5BB409210C}"/>
+    <hyperlink ref="H21" r:id="rId13" xr:uid="{FD8E0303-E96C-48CB-9D75-78033B6BD3D7}"/>
+    <hyperlink ref="H14" r:id="rId14" xr:uid="{30CC3CB7-1AAB-423C-B83D-2EE5B8956A90}"/>
+  </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -7172,8 +7749,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="25" customFormat="1" ht="58.15" customHeight="1">
-      <c r="A2" s="141" t="s">
+    <row r="2" spans="1:10" s="25" customFormat="1" ht="58.35" customHeight="1">
+      <c r="A2" s="157" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -7198,8 +7775,8 @@
       </c>
       <c r="J2" s="24"/>
     </row>
-    <row r="3" spans="1:10" s="25" customFormat="1" ht="124.9">
-      <c r="A3" s="141"/>
+    <row r="3" spans="1:10" s="25" customFormat="1" ht="126">
+      <c r="A3" s="157"/>
       <c r="B3" s="19" t="s">
         <v>35</v>
       </c>
@@ -7224,8 +7801,8 @@
       </c>
       <c r="J3" s="31"/>
     </row>
-    <row r="4" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A4" s="141"/>
+    <row r="4" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A4" s="157"/>
       <c r="B4" s="19" t="s">
         <v>39</v>
       </c>
@@ -7250,8 +7827,8 @@
       </c>
       <c r="J4" s="31"/>
     </row>
-    <row r="5" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A5" s="141"/>
+    <row r="5" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A5" s="157"/>
       <c r="B5" s="19" t="s">
         <v>43</v>
       </c>
@@ -7276,8 +7853,8 @@
       </c>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A6" s="141"/>
+    <row r="6" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A6" s="157"/>
       <c r="B6" s="19" t="s">
         <v>47</v>
       </c>
@@ -7302,8 +7879,8 @@
       </c>
       <c r="J6" s="31"/>
     </row>
-    <row r="7" spans="1:10" s="25" customFormat="1" ht="78">
-      <c r="A7" s="141"/>
+    <row r="7" spans="1:10" s="25" customFormat="1" ht="78.75">
+      <c r="A7" s="157"/>
       <c r="B7" s="19" t="s">
         <v>50</v>
       </c>
@@ -7328,8 +7905,8 @@
       </c>
       <c r="J7" s="31"/>
     </row>
-    <row r="8" spans="1:10" s="25" customFormat="1" ht="124.9">
-      <c r="A8" s="141"/>
+    <row r="8" spans="1:10" s="25" customFormat="1" ht="126">
+      <c r="A8" s="157"/>
       <c r="B8" s="19" t="s">
         <v>54</v>
       </c>
@@ -7355,7 +7932,7 @@
       <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:10" s="25" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A9" s="141" t="s">
+      <c r="A9" s="157" t="s">
         <v>58</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -7382,8 +7959,8 @@
       </c>
       <c r="J9" s="31"/>
     </row>
-    <row r="10" spans="1:10" s="25" customFormat="1" ht="78">
-      <c r="A10" s="141"/>
+    <row r="10" spans="1:10" s="25" customFormat="1" ht="78.75">
+      <c r="A10" s="157"/>
       <c r="B10" s="19" t="s">
         <v>62</v>
       </c>
@@ -7408,8 +7985,8 @@
       </c>
       <c r="J10" s="31"/>
     </row>
-    <row r="11" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A11" s="141"/>
+    <row r="11" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A11" s="157"/>
       <c r="B11" s="19" t="s">
         <v>66</v>
       </c>
@@ -7434,8 +8011,8 @@
       </c>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A12" s="141"/>
+    <row r="12" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A12" s="157"/>
       <c r="B12" s="19" t="s">
         <v>69</v>
       </c>
@@ -7461,7 +8038,7 @@
       <c r="J12" s="31"/>
     </row>
     <row r="13" spans="1:10" s="25" customFormat="1" ht="42">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="19"/>
@@ -7479,7 +8056,7 @@
       <c r="J13" s="31"/>
     </row>
     <row r="14" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A14" s="141" t="s">
+      <c r="A14" s="157" t="s">
         <v>76</v>
       </c>
       <c r="B14" s="19" t="s">
@@ -7506,8 +8083,8 @@
       </c>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" s="25" customFormat="1" ht="15.6">
-      <c r="A15" s="141"/>
+    <row r="15" spans="1:10" s="25" customFormat="1" ht="15.75">
+      <c r="A15" s="157"/>
       <c r="B15" s="19" t="s">
         <v>80</v>
       </c>
@@ -7528,8 +8105,8 @@
       <c r="I15" s="28"/>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" s="25" customFormat="1" ht="15.6">
-      <c r="A16" s="141"/>
+    <row r="16" spans="1:10" s="25" customFormat="1" ht="15.75">
+      <c r="A16" s="157"/>
       <c r="B16" s="19" t="s">
         <v>82</v>
       </c>
@@ -7550,8 +8127,8 @@
       <c r="I16" s="28"/>
       <c r="J16" s="32"/>
     </row>
-    <row r="17" spans="1:10" s="25" customFormat="1" ht="94.15" thickBot="1">
-      <c r="A17" s="141"/>
+    <row r="17" spans="1:10" s="25" customFormat="1" ht="95.25" thickBot="1">
+      <c r="A17" s="157"/>
       <c r="B17" s="19" t="s">
         <v>84</v>
       </c>
@@ -7576,8 +8153,8 @@
       </c>
       <c r="J17" s="32"/>
     </row>
-    <row r="18" spans="1:10" s="25" customFormat="1" ht="94.15" thickBot="1">
-      <c r="A18" s="141"/>
+    <row r="18" spans="1:10" s="25" customFormat="1" ht="95.25" thickBot="1">
+      <c r="A18" s="157"/>
       <c r="B18" s="19" t="s">
         <v>87</v>
       </c>
@@ -7603,7 +8180,7 @@
       <c r="J18" s="32"/>
     </row>
     <row r="19" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1" thickBot="1">
-      <c r="A19" s="141" t="s">
+      <c r="A19" s="157" t="s">
         <v>91</v>
       </c>
       <c r="B19" s="19" t="s">
@@ -7630,8 +8207,8 @@
       </c>
       <c r="J19" s="32"/>
     </row>
-    <row r="20" spans="1:10" s="25" customFormat="1" ht="78">
-      <c r="A20" s="141"/>
+    <row r="20" spans="1:10" s="25" customFormat="1" ht="78.75">
+      <c r="A20" s="157"/>
       <c r="B20" s="19" t="s">
         <v>96</v>
       </c>
@@ -7652,8 +8229,8 @@
       <c r="I20" s="28"/>
       <c r="J20" s="32"/>
     </row>
-    <row r="21" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A21" s="141"/>
+    <row r="21" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A21" s="157"/>
       <c r="B21" s="19" t="s">
         <v>98</v>
       </c>
@@ -7678,8 +8255,8 @@
       </c>
       <c r="J21" s="32"/>
     </row>
-    <row r="22" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A22" s="141"/>
+    <row r="22" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A22" s="157"/>
       <c r="B22" s="19" t="s">
         <v>102</v>
       </c>
@@ -7701,7 +8278,7 @@
       <c r="J22" s="32"/>
     </row>
     <row r="23" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A23" s="141" t="s">
+      <c r="A23" s="157" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="19" t="s">
@@ -7728,8 +8305,8 @@
       </c>
       <c r="J23" s="32"/>
     </row>
-    <row r="24" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A24" s="141"/>
+    <row r="24" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A24" s="157"/>
       <c r="B24" s="19" t="s">
         <v>108</v>
       </c>
@@ -7754,8 +8331,8 @@
       </c>
       <c r="J24" s="32"/>
     </row>
-    <row r="25" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A25" s="141"/>
+    <row r="25" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A25" s="157"/>
       <c r="B25" s="19" t="s">
         <v>110</v>
       </c>
@@ -7776,8 +8353,8 @@
       <c r="I25" s="28"/>
       <c r="J25" s="32"/>
     </row>
-    <row r="26" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A26" s="141"/>
+    <row r="26" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A26" s="157"/>
       <c r="B26" s="19" t="s">
         <v>113</v>
       </c>
@@ -7799,7 +8376,7 @@
       <c r="J26" s="32"/>
     </row>
     <row r="27" spans="1:10" s="25" customFormat="1" ht="67.5" customHeight="1">
-      <c r="A27" s="141" t="s">
+      <c r="A27" s="157" t="s">
         <v>115</v>
       </c>
       <c r="B27" s="19" t="s">
@@ -7822,8 +8399,8 @@
       <c r="I27" s="28"/>
       <c r="J27" s="32"/>
     </row>
-    <row r="28" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A28" s="141"/>
+    <row r="28" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A28" s="157"/>
       <c r="B28" s="19" t="s">
         <v>118</v>
       </c>
@@ -7843,7 +8420,7 @@
       <c r="J28" s="32"/>
     </row>
     <row r="29" spans="1:10" s="25" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A29" s="141" t="s">
+      <c r="A29" s="157" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="19" t="s">
@@ -7865,7 +8442,7 @@
       <c r="J29" s="32"/>
     </row>
     <row r="30" spans="1:10" s="25" customFormat="1" ht="80.25" customHeight="1">
-      <c r="A30" s="141"/>
+      <c r="A30" s="157"/>
       <c r="B30" s="19" t="s">
         <v>123</v>
       </c>
@@ -7885,7 +8462,7 @@
       <c r="J30" s="32"/>
     </row>
     <row r="31" spans="1:10" s="25" customFormat="1" ht="79.5" customHeight="1">
-      <c r="A31" s="141" t="s">
+      <c r="A31" s="157" t="s">
         <v>125</v>
       </c>
       <c r="B31" s="19" t="s">
@@ -7912,8 +8489,8 @@
       </c>
       <c r="J31" s="32"/>
     </row>
-    <row r="32" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A32" s="141"/>
+    <row r="32" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A32" s="157"/>
       <c r="B32" s="19" t="s">
         <v>129</v>
       </c>
@@ -7938,8 +8515,8 @@
       </c>
       <c r="J32" s="32"/>
     </row>
-    <row r="33" spans="1:10" s="25" customFormat="1" ht="78">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:10" s="25" customFormat="1" ht="78.75">
+      <c r="A33" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="19" t="s">
@@ -7967,7 +8544,7 @@
       <c r="J33" s="32"/>
     </row>
     <row r="34" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A34" s="141" t="s">
+      <c r="A34" s="157" t="s">
         <v>137</v>
       </c>
       <c r="B34" s="19" t="s">
@@ -7994,8 +8571,8 @@
       </c>
       <c r="J34" s="32"/>
     </row>
-    <row r="35" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A35" s="141"/>
+    <row r="35" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A35" s="157"/>
       <c r="B35" s="19" t="s">
         <v>142</v>
       </c>
@@ -8020,8 +8597,8 @@
       </c>
       <c r="J35" s="32"/>
     </row>
-    <row r="36" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A36" s="141"/>
+    <row r="36" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A36" s="157"/>
       <c r="B36" s="19" t="s">
         <v>145</v>
       </c>
@@ -8047,7 +8624,7 @@
       <c r="J36" s="32"/>
     </row>
     <row r="37" spans="1:10" s="25" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A37" s="141" t="s">
+      <c r="A37" s="157" t="s">
         <v>148</v>
       </c>
       <c r="B37" s="19" t="s">
@@ -8070,8 +8647,8 @@
       <c r="I37" s="28"/>
       <c r="J37" s="32"/>
     </row>
-    <row r="38" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A38" s="141"/>
+    <row r="38" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A38" s="157"/>
       <c r="B38" s="19" t="s">
         <v>151</v>
       </c>
@@ -8097,7 +8674,7 @@
       <c r="J38" s="32"/>
     </row>
     <row r="39" spans="1:10" s="25" customFormat="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B39" s="19"/>
@@ -8114,8 +8691,8 @@
       <c r="I39" s="28"/>
       <c r="J39" s="32"/>
     </row>
-    <row r="40" spans="1:10" s="25" customFormat="1" ht="58.9" customHeight="1">
-      <c r="A40" s="141" t="s">
+    <row r="40" spans="1:10" s="25" customFormat="1" ht="59.1" customHeight="1">
+      <c r="A40" s="157" t="s">
         <v>156</v>
       </c>
       <c r="B40" s="19" t="s">
@@ -8142,8 +8719,8 @@
       </c>
       <c r="J40" s="32"/>
     </row>
-    <row r="41" spans="1:10" s="25" customFormat="1" ht="47.45" thickBot="1">
-      <c r="A41" s="141"/>
+    <row r="41" spans="1:10" s="25" customFormat="1" ht="32.25" thickBot="1">
+      <c r="A41" s="157"/>
       <c r="B41" s="19" t="s">
         <v>160</v>
       </c>
@@ -8164,8 +8741,8 @@
       <c r="I41" s="28"/>
       <c r="J41" s="32"/>
     </row>
-    <row r="42" spans="1:10" s="25" customFormat="1" ht="31.9" thickBot="1">
-      <c r="A42" s="141"/>
+    <row r="42" spans="1:10" s="25" customFormat="1" ht="32.25" thickBot="1">
+      <c r="A42" s="157"/>
       <c r="B42" s="19" t="s">
         <v>162</v>
       </c>
@@ -8188,8 +8765,8 @@
       <c r="I42" s="30"/>
       <c r="J42" s="32"/>
     </row>
-    <row r="43" spans="1:10" s="25" customFormat="1" ht="63" thickBot="1">
-      <c r="A43" s="141"/>
+    <row r="43" spans="1:10" s="25" customFormat="1" ht="63.75" thickBot="1">
+      <c r="A43" s="157"/>
       <c r="B43" s="19" t="s">
         <v>165</v>
       </c>
@@ -8210,8 +8787,8 @@
       <c r="I43" s="30"/>
       <c r="J43" s="32"/>
     </row>
-    <row r="44" spans="1:10" s="25" customFormat="1" ht="94.15" thickBot="1">
-      <c r="A44" s="141"/>
+    <row r="44" spans="1:10" s="25" customFormat="1" ht="95.25" thickBot="1">
+      <c r="A44" s="157"/>
       <c r="B44" s="19" t="s">
         <v>167</v>
       </c>
@@ -8232,8 +8809,8 @@
       <c r="I44" s="120"/>
       <c r="J44" s="32"/>
     </row>
-    <row r="45" spans="1:10" s="25" customFormat="1" ht="63" thickBot="1">
-      <c r="A45" s="141"/>
+    <row r="45" spans="1:10" s="25" customFormat="1" ht="63.75" thickBot="1">
+      <c r="A45" s="157"/>
       <c r="B45" s="19" t="s">
         <v>169</v>
       </c>
@@ -8254,22 +8831,22 @@
       <c r="I45" s="126"/>
       <c r="J45" s="37"/>
     </row>
-    <row r="46" spans="1:10" ht="21.6" thickBot="1">
+    <row r="46" spans="1:10" ht="21.75" thickBot="1">
       <c r="I46" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
     <mergeCell ref="A40:A45"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G45 H44" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -8348,7 +8925,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="158" t="s">
         <v>171</v>
       </c>
       <c r="B2" s="44" t="s">
@@ -8377,8 +8954,8 @@
       </c>
       <c r="J2" s="51"/>
     </row>
-    <row r="3" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A3" s="158"/>
       <c r="B3" s="44" t="s">
         <v>177</v>
       </c>
@@ -8401,8 +8978,8 @@
       <c r="I3" s="30"/>
       <c r="J3" s="31"/>
     </row>
-    <row r="4" spans="1:10" s="25" customFormat="1" ht="66.599999999999994">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" s="25" customFormat="1" ht="64.5">
+      <c r="A4" s="158"/>
       <c r="B4" s="44" t="s">
         <v>179</v>
       </c>
@@ -8429,8 +9006,8 @@
       </c>
       <c r="J4" s="31"/>
     </row>
-    <row r="5" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" s="25" customFormat="1" ht="113.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="44" t="s">
         <v>182</v>
       </c>
@@ -8457,8 +9034,8 @@
       </c>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A6" s="158"/>
       <c r="B6" s="44" t="s">
         <v>185</v>
       </c>
@@ -8485,8 +9062,8 @@
       </c>
       <c r="J6" s="31"/>
     </row>
-    <row r="7" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A7" s="158"/>
       <c r="B7" s="44" t="s">
         <v>189</v>
       </c>
@@ -8513,8 +9090,8 @@
       </c>
       <c r="J7" s="31"/>
     </row>
-    <row r="8" spans="1:10" s="25" customFormat="1" ht="140.44999999999999">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" s="25" customFormat="1" ht="141.75">
+      <c r="A8" s="158"/>
       <c r="B8" s="44" t="s">
         <v>192</v>
       </c>
@@ -8537,8 +9114,8 @@
       <c r="I8" s="30"/>
       <c r="J8" s="31"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A9" s="158"/>
       <c r="B9" s="44" t="s">
         <v>194</v>
       </c>
@@ -8561,8 +9138,8 @@
       <c r="I9" s="30"/>
       <c r="J9" s="31"/>
     </row>
-    <row r="10" spans="1:10" s="25" customFormat="1" ht="109.15">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A10" s="158"/>
       <c r="B10" s="44" t="s">
         <v>196</v>
       </c>
@@ -8589,8 +9166,8 @@
       </c>
       <c r="J10" s="31"/>
     </row>
-    <row r="11" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A11" s="158"/>
       <c r="B11" s="44" t="s">
         <v>200</v>
       </c>
@@ -8617,8 +9194,8 @@
       </c>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A12" s="158"/>
       <c r="B12" s="44" t="s">
         <v>202</v>
       </c>
@@ -8641,8 +9218,8 @@
       <c r="I12" s="30"/>
       <c r="J12" s="31"/>
     </row>
-    <row r="13" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A13" s="158"/>
       <c r="B13" s="44" t="s">
         <v>204</v>
       </c>
@@ -8666,7 +9243,7 @@
       <c r="J13" s="31"/>
     </row>
     <row r="14" spans="1:10" s="25" customFormat="1" ht="111" customHeight="1">
-      <c r="A14" s="142" t="s">
+      <c r="A14" s="158" t="s">
         <v>206</v>
       </c>
       <c r="B14" s="44" t="s">
@@ -8685,16 +9262,20 @@
         <v>209</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
+        <v>26</v>
+      </c>
+      <c r="H14" s="156" t="s">
+        <v>210</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>211</v>
+      </c>
       <c r="J14" s="31"/>
     </row>
-    <row r="15" spans="1:10" s="25" customFormat="1" ht="78">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" s="25" customFormat="1" ht="78.75">
+      <c r="A15" s="158"/>
       <c r="B15" s="44" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C15" s="52">
         <v>1</v>
@@ -8703,10 +9284,10 @@
         <v>304</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>75</v>
@@ -8715,10 +9296,10 @@
       <c r="I15" s="30"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A16" s="142"/>
+    <row r="16" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A16" s="158"/>
       <c r="B16" s="44" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C16" s="52">
         <v>1</v>
@@ -8728,7 +9309,7 @@
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="29" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G16" s="28" t="s">
         <v>75</v>
@@ -8737,10 +9318,10 @@
       <c r="I16" s="30"/>
       <c r="J16" s="31"/>
     </row>
-    <row r="17" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A17" s="158"/>
       <c r="B17" s="44" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C17" s="54">
         <v>3</v>
@@ -8749,10 +9330,10 @@
         <v>308</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>75</v>
@@ -8761,10 +9342,10 @@
       <c r="I17" s="30"/>
       <c r="J17" s="31"/>
     </row>
-    <row r="18" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A18" s="142"/>
+    <row r="18" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A18" s="158"/>
       <c r="B18" s="44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C18" s="54">
         <v>3</v>
@@ -8773,10 +9354,10 @@
         <v>319</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F18" s="29" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>75</v>
@@ -8785,10 +9366,10 @@
       <c r="I18" s="30"/>
       <c r="J18" s="31"/>
     </row>
-    <row r="19" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A19" s="142"/>
+    <row r="19" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A19" s="158"/>
       <c r="B19" s="44" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C19" s="54">
         <v>3</v>
@@ -8797,10 +9378,10 @@
         <v>308</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>75</v>
@@ -8809,10 +9390,10 @@
       <c r="I19" s="30"/>
       <c r="J19" s="31"/>
     </row>
-    <row r="20" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A20" s="142"/>
+    <row r="20" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A20" s="158"/>
       <c r="B20" s="44" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="54">
         <v>3</v>
@@ -8821,10 +9402,10 @@
         <v>308</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>75</v>
@@ -8834,11 +9415,11 @@
       <c r="J20" s="31"/>
     </row>
     <row r="21" spans="1:10" s="25" customFormat="1" ht="79.5" customHeight="1">
-      <c r="A21" s="142" t="s">
-        <v>227</v>
+      <c r="A21" s="158" t="s">
+        <v>229</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C21" s="52">
         <v>1</v>
@@ -8847,10 +9428,10 @@
         <v>330</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>75</v>
@@ -8859,10 +9440,10 @@
       <c r="I21" s="30"/>
       <c r="J21" s="31"/>
     </row>
-    <row r="22" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A22" s="142"/>
+    <row r="22" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A22" s="158"/>
       <c r="B22" s="44" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C22" s="55">
         <v>2</v>
@@ -8871,10 +9452,10 @@
         <v>308</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G22" s="28" t="s">
         <v>75</v>
@@ -8883,10 +9464,10 @@
       <c r="I22" s="30"/>
       <c r="J22" s="31"/>
     </row>
-    <row r="23" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A23" s="142"/>
+    <row r="23" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A23" s="158"/>
       <c r="B23" s="44" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C23" s="55">
         <v>2</v>
@@ -8895,10 +9476,10 @@
         <v>287</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>75</v>
@@ -8908,11 +9489,11 @@
       <c r="J23" s="31"/>
     </row>
     <row r="24" spans="1:10" s="25" customFormat="1" ht="95.25" customHeight="1">
-      <c r="A24" s="142" t="s">
-        <v>237</v>
+      <c r="A24" s="158" t="s">
+        <v>239</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C24" s="55">
         <v>2</v>
@@ -8924,19 +9505,23 @@
         <v>173</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+        <v>26</v>
+      </c>
+      <c r="H24" s="156" t="s">
+        <v>242</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>243</v>
+      </c>
       <c r="J24" s="31"/>
     </row>
-    <row r="25" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A25" s="142"/>
+    <row r="25" spans="1:10" s="25" customFormat="1" ht="64.5">
+      <c r="A25" s="158"/>
       <c r="B25" s="44" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C25" s="55">
         <v>2</v>
@@ -8948,19 +9533,23 @@
         <v>173</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
+        <v>26</v>
+      </c>
+      <c r="H25" s="156" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>246</v>
+      </c>
       <c r="J25" s="31"/>
     </row>
-    <row r="26" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A26" s="142"/>
+    <row r="26" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A26" s="158"/>
       <c r="B26" s="44" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C26" s="55">
         <v>2</v>
@@ -8972,19 +9561,17 @@
         <v>173</v>
       </c>
       <c r="F26" s="29" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G26" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
       <c r="J26" s="31"/>
     </row>
-    <row r="27" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A27" s="142"/>
+    <row r="27" spans="1:10" s="25" customFormat="1" ht="64.5">
+      <c r="A27" s="158"/>
       <c r="B27" s="44" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C27" s="55">
         <v>2</v>
@@ -8996,19 +9583,23 @@
         <v>173</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
+        <v>26</v>
+      </c>
+      <c r="H27" s="156" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="30" t="s">
+        <v>251</v>
+      </c>
       <c r="J27" s="31"/>
     </row>
-    <row r="28" spans="1:10" s="25" customFormat="1" ht="109.15">
-      <c r="A28" s="142"/>
+    <row r="28" spans="1:10" s="25" customFormat="1" ht="110.25">
+      <c r="A28" s="158"/>
       <c r="B28" s="44" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C28" s="55">
         <v>2</v>
@@ -9020,21 +9611,21 @@
         <v>173</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H28" s="28"/>
       <c r="I28" s="28"/>
       <c r="J28" s="32"/>
     </row>
     <row r="29" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A29" s="142" t="s">
-        <v>248</v>
+      <c r="A29" s="158" t="s">
+        <v>254</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C29" s="52">
         <v>1</v>
@@ -9046,19 +9637,19 @@
         <v>173</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="H29" s="28"/>
       <c r="I29" s="28"/>
       <c r="J29" s="32"/>
     </row>
-    <row r="30" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A30" s="142"/>
+    <row r="30" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A30" s="158"/>
       <c r="B30" s="44" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C30" s="52">
         <v>1</v>
@@ -9070,7 +9661,7 @@
         <v>173</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G30" s="28" t="s">
         <v>75</v>
@@ -9079,10 +9670,10 @@
       <c r="I30" s="28"/>
       <c r="J30" s="32"/>
     </row>
-    <row r="31" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A31" s="142"/>
+    <row r="31" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A31" s="158"/>
       <c r="B31" s="44" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C31" s="52">
         <v>1</v>
@@ -9094,19 +9685,21 @@
         <v>173</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G31" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="I31" s="28" t="s">
+        <v>261</v>
+      </c>
       <c r="J31" s="32"/>
     </row>
-    <row r="32" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A32" s="142"/>
+    <row r="32" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A32" s="158"/>
       <c r="B32" s="44" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C32" s="52">
         <v>1</v>
@@ -9115,22 +9708,24 @@
         <v>16</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F32" s="29" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="I32" s="28" t="s">
+        <v>264</v>
+      </c>
       <c r="J32" s="32"/>
     </row>
-    <row r="33" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A33" s="142"/>
+    <row r="33" spans="1:10" s="25" customFormat="1" ht="32.25">
+      <c r="A33" s="158"/>
       <c r="B33" s="44" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C33" s="52">
         <v>1</v>
@@ -9139,22 +9734,26 @@
         <v>304</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H33" s="154" t="s">
+        <v>268</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>269</v>
+      </c>
       <c r="J33" s="32"/>
     </row>
-    <row r="34" spans="1:10" s="25" customFormat="1" ht="62.45">
-      <c r="A34" s="142"/>
+    <row r="34" spans="1:10" s="25" customFormat="1" ht="63">
+      <c r="A34" s="158"/>
       <c r="B34" s="44" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C34" s="52">
         <v>1</v>
@@ -9166,7 +9765,7 @@
         <v>173</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G34" s="28" t="s">
         <v>75</v>
@@ -9175,10 +9774,10 @@
       <c r="I34" s="28"/>
       <c r="J34" s="32"/>
     </row>
-    <row r="35" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A35" s="142"/>
+    <row r="35" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A35" s="158"/>
       <c r="B35" s="44" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C35" s="55">
         <v>2</v>
@@ -9187,10 +9786,10 @@
         <v>308</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="G35" s="28" t="s">
         <v>75</v>
@@ -9200,11 +9799,11 @@
       <c r="J35" s="32"/>
     </row>
     <row r="36" spans="1:10" s="25" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A36" s="142" t="s">
-        <v>264</v>
+      <c r="A36" s="158" t="s">
+        <v>274</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="C36" s="55">
         <v>2</v>
@@ -9213,10 +9812,10 @@
         <v>308</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="G36" s="28" t="s">
         <v>75</v>
@@ -9225,10 +9824,10 @@
       <c r="I36" s="28"/>
       <c r="J36" s="32"/>
     </row>
-    <row r="37" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A37" s="142"/>
+    <row r="37" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A37" s="158"/>
       <c r="B37" s="44" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C37" s="55">
         <v>2</v>
@@ -9237,10 +9836,10 @@
         <v>330</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="G37" s="28" t="s">
         <v>75</v>
@@ -9249,10 +9848,10 @@
       <c r="I37" s="28"/>
       <c r="J37" s="32"/>
     </row>
-    <row r="38" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A38" s="142"/>
+    <row r="38" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A38" s="158"/>
       <c r="B38" s="44" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C38" s="55">
         <v>2</v>
@@ -9261,10 +9860,10 @@
         <v>310</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G38" s="28" t="s">
         <v>75</v>
@@ -9274,11 +9873,11 @@
       <c r="J38" s="32"/>
     </row>
     <row r="39" spans="1:10" s="25" customFormat="1" ht="48" customHeight="1">
-      <c r="A39" s="142" t="s">
-        <v>272</v>
+      <c r="A39" s="158" t="s">
+        <v>282</v>
       </c>
       <c r="B39" s="44" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C39" s="52">
         <v>1</v>
@@ -9287,10 +9886,10 @@
         <v>287</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="G39" s="28" t="s">
         <v>75</v>
@@ -9299,10 +9898,10 @@
       <c r="I39" s="28"/>
       <c r="J39" s="32"/>
     </row>
-    <row r="40" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A40" s="142"/>
+    <row r="40" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A40" s="158"/>
       <c r="B40" s="44" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C40" s="52">
         <v>1</v>
@@ -9311,10 +9910,10 @@
         <v>287</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G40" s="28" t="s">
         <v>75</v>
@@ -9323,10 +9922,10 @@
       <c r="I40" s="28"/>
       <c r="J40" s="32"/>
     </row>
-    <row r="41" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A41" s="142"/>
+    <row r="41" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A41" s="158"/>
       <c r="B41" s="44" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C41" s="52">
         <v>1</v>
@@ -9335,10 +9934,10 @@
         <v>287</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G41" s="28" t="s">
         <v>75</v>
@@ -9347,10 +9946,10 @@
       <c r="I41" s="28"/>
       <c r="J41" s="32"/>
     </row>
-    <row r="42" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A42" s="142"/>
+    <row r="42" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A42" s="158"/>
       <c r="B42" s="44" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C42" s="52">
         <v>1</v>
@@ -9359,10 +9958,10 @@
         <v>523</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G42" s="28" t="s">
         <v>75</v>
@@ -9371,10 +9970,10 @@
       <c r="I42" s="28"/>
       <c r="J42" s="32"/>
     </row>
-    <row r="43" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A43" s="142"/>
+    <row r="43" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A43" s="158"/>
       <c r="B43" s="44" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C43" s="55">
         <v>2</v>
@@ -9383,10 +9982,10 @@
         <v>256</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G43" s="28" t="s">
         <v>75</v>
@@ -9395,10 +9994,10 @@
       <c r="I43" s="28"/>
       <c r="J43" s="32"/>
     </row>
-    <row r="44" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A44" s="142"/>
+    <row r="44" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A44" s="158"/>
       <c r="B44" s="44" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C44" s="55">
         <v>2</v>
@@ -9407,10 +10006,10 @@
         <v>310</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="G44" s="28" t="s">
         <v>75</v>
@@ -9420,11 +10019,11 @@
       <c r="J44" s="32"/>
     </row>
     <row r="45" spans="1:10" s="25" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A45" s="142" t="s">
-        <v>286</v>
+      <c r="A45" s="158" t="s">
+        <v>296</v>
       </c>
       <c r="B45" s="44" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C45" s="52">
         <v>1</v>
@@ -9433,10 +10032,10 @@
         <v>613</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="G45" s="28" t="s">
         <v>75</v>
@@ -9445,10 +10044,10 @@
       <c r="I45" s="28"/>
       <c r="J45" s="32"/>
     </row>
-    <row r="46" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A46" s="142"/>
+    <row r="46" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A46" s="158"/>
       <c r="B46" s="44" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C46" s="55">
         <v>2</v>
@@ -9457,10 +10056,10 @@
         <v>320</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G46" s="28" t="s">
         <v>75</v>
@@ -9469,10 +10068,10 @@
       <c r="I46" s="28"/>
       <c r="J46" s="32"/>
     </row>
-    <row r="47" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A47" s="142"/>
+    <row r="47" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A47" s="158"/>
       <c r="B47" s="44" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C47" s="55">
         <v>2</v>
@@ -9481,10 +10080,10 @@
         <v>326</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="G47" s="28" t="s">
         <v>75</v>
@@ -9493,10 +10092,10 @@
       <c r="I47" s="28"/>
       <c r="J47" s="32"/>
     </row>
-    <row r="48" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A48" s="142"/>
+    <row r="48" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A48" s="158"/>
       <c r="B48" s="44" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C48" s="55">
         <v>2</v>
@@ -9505,10 +10104,10 @@
         <v>287</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="G48" s="28" t="s">
         <v>75</v>
@@ -9517,10 +10116,10 @@
       <c r="I48" s="28"/>
       <c r="J48" s="32"/>
     </row>
-    <row r="49" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A49" s="142"/>
+    <row r="49" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A49" s="158"/>
       <c r="B49" s="44" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C49" s="55">
         <v>2</v>
@@ -9529,10 +10128,10 @@
         <v>287</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G49" s="28" t="s">
         <v>75</v>
@@ -9541,10 +10140,10 @@
       <c r="I49" s="28"/>
       <c r="J49" s="32"/>
     </row>
-    <row r="50" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A50" s="142"/>
+    <row r="50" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A50" s="158"/>
       <c r="B50" s="44" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C50" s="55">
         <v>2</v>
@@ -9553,10 +10152,10 @@
         <v>613</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G50" s="28" t="s">
         <v>75</v>
@@ -9565,10 +10164,10 @@
       <c r="I50" s="28"/>
       <c r="J50" s="32"/>
     </row>
-    <row r="51" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A51" s="142"/>
+    <row r="51" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A51" s="158"/>
       <c r="B51" s="44" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C51" s="54">
         <v>3</v>
@@ -9577,10 +10176,10 @@
         <v>308</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G51" s="28" t="s">
         <v>75</v>
@@ -9590,11 +10189,11 @@
       <c r="J51" s="32"/>
     </row>
     <row r="52" spans="1:10" s="25" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A52" s="142" t="s">
-        <v>305</v>
+      <c r="A52" s="158" t="s">
+        <v>315</v>
       </c>
       <c r="B52" s="44" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C52" s="55">
         <v>2</v>
@@ -9603,10 +10202,10 @@
         <v>320</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="G52" s="28" t="s">
         <v>75</v>
@@ -9615,10 +10214,10 @@
       <c r="I52" s="28"/>
       <c r="J52" s="32"/>
     </row>
-    <row r="53" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A53" s="142"/>
+    <row r="53" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A53" s="158"/>
       <c r="B53" s="44" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C53" s="55">
         <v>2</v>
@@ -9627,10 +10226,10 @@
         <v>330</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G53" s="28" t="s">
         <v>75</v>
@@ -9639,10 +10238,10 @@
       <c r="I53" s="28"/>
       <c r="J53" s="32"/>
     </row>
-    <row r="54" spans="1:10" s="25" customFormat="1" ht="31.15">
-      <c r="A54" s="142"/>
+    <row r="54" spans="1:10" s="25" customFormat="1" ht="31.5">
+      <c r="A54" s="158"/>
       <c r="B54" s="44" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C54" s="55">
         <v>2</v>
@@ -9651,10 +10250,10 @@
         <v>327</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="G54" s="28" t="s">
         <v>75</v>
@@ -9664,23 +10263,23 @@
       <c r="J54" s="32"/>
     </row>
     <row r="55" spans="1:10" s="25" customFormat="1" ht="79.5" customHeight="1">
-      <c r="A55" s="142" t="s">
-        <v>313</v>
+      <c r="A55" s="158" t="s">
+        <v>323</v>
       </c>
       <c r="B55" s="44" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D55" s="53">
         <v>287</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="G55" s="28" t="s">
         <v>75</v>
@@ -9689,46 +10288,48 @@
       <c r="I55" s="28"/>
       <c r="J55" s="32"/>
     </row>
-    <row r="56" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A56" s="142"/>
+    <row r="56" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A56" s="158"/>
       <c r="B56" s="44" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D56" s="53">
         <v>255</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
+      <c r="I56" s="28" t="s">
+        <v>330</v>
+      </c>
       <c r="J56" s="32"/>
     </row>
-    <row r="57" spans="1:10" s="25" customFormat="1" ht="46.9">
-      <c r="A57" s="142"/>
+    <row r="57" spans="1:10" s="25" customFormat="1" ht="47.25">
+      <c r="A57" s="158"/>
       <c r="B57" s="44" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D57" s="53">
         <v>522</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="G57" s="28" t="s">
         <v>75</v>
@@ -9737,20 +10338,20 @@
       <c r="I57" s="28"/>
       <c r="J57" s="32"/>
     </row>
-    <row r="58" spans="1:10" s="25" customFormat="1" ht="93.6">
-      <c r="A58" s="142"/>
+    <row r="58" spans="1:10" s="25" customFormat="1" ht="94.5">
+      <c r="A58" s="158"/>
       <c r="B58" s="44" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C58" s="56" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="D58" s="57">
         <v>798</v>
       </c>
       <c r="E58" s="34"/>
       <c r="F58" s="36" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="G58" s="120" t="s">
         <v>75</v>
@@ -9761,16 +10362,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A29:A35"/>
     <mergeCell ref="A36:A38"/>
     <mergeCell ref="A39:A44"/>
     <mergeCell ref="A45:A51"/>
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="A29:A35"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G58" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -9780,6 +10381,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{541BF414-FC30-B842-96C0-5FA0634316AB}"/>
+    <hyperlink ref="H24" r:id="rId2" xr:uid="{5587BAF7-3EA4-46DF-B44E-0B53AD135826}"/>
+    <hyperlink ref="H25" r:id="rId3" xr:uid="{5C9774C3-6953-4B7F-B3F9-7D2812B9F754}"/>
+    <hyperlink ref="H27" r:id="rId4" xr:uid="{223D3802-AAB8-4B5D-8D59-9D72A72C0262}"/>
+    <hyperlink ref="H14" r:id="rId5" xr:uid="{8B2A904E-6E6F-4B4A-84FA-CE134CEB600B}"/>
+    <hyperlink ref="H33" r:id="rId6" xr:uid="{226B78AC-7FC5-4C0B-8261-7EB16C398B43}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9840,11 +10446,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="42">
-      <c r="A2" s="1" t="s">
-        <v>324</v>
+      <c r="A2" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -9854,19 +10460,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="133" t="s">
-        <v>326</v>
-      </c>
-      <c r="G2" s="49"/>
+        <v>337</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>26</v>
+      </c>
       <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+      <c r="I2" s="49" t="s">
+        <v>338</v>
+      </c>
       <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A3" s="142" t="s">
-        <v>327</v>
+      <c r="A3" s="158" t="s">
+        <v>339</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -9878,17 +10488,23 @@
         <v>7.1</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>329</v>
-      </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+        <v>341</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="154" t="s">
+        <v>342</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>343</v>
+      </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="46.9">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="47.25">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -9900,17 +10516,23 @@
         <v>7.1</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
+        <v>345</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="154" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>346</v>
+      </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="46.9">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C5" s="66">
         <v>1</v>
@@ -9922,17 +10544,21 @@
         <v>7.1</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="G5" s="28"/>
+        <v>348</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+      <c r="I5" s="28" t="s">
+        <v>349</v>
+      </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="62.45">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="63">
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C6" s="68">
         <v>2</v>
@@ -9944,19 +10570,25 @@
         <v>7.1</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>335</v>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
+        <v>351</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="154" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>352</v>
+      </c>
       <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10" ht="79.5" customHeight="1">
-      <c r="A7" s="142" t="s">
-        <v>336</v>
+      <c r="A7" s="158" t="s">
+        <v>353</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C7" s="66">
         <v>1</v>
@@ -9968,17 +10600,21 @@
         <v>7.1</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>338</v>
-      </c>
-      <c r="G7" s="28"/>
+        <v>355</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
+      <c r="I7" s="28" t="s">
+        <v>356</v>
+      </c>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="109.15">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="110.25">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -9990,17 +10626,23 @@
         <v>7.2</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
+        <v>358</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>342</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>359</v>
+      </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="62.45">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="63">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C9" s="68">
         <v>2</v>
@@ -10010,17 +10652,19 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="29" t="s">
-        <v>342</v>
-      </c>
-      <c r="G9" s="28"/>
+        <v>361</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H9" s="28"/>
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="31.15">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="31.5">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C10" s="68">
         <v>2</v>
@@ -10032,19 +10676,21 @@
         <v>7.1</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>344</v>
-      </c>
-      <c r="G10" s="28"/>
+        <v>363</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H10" s="28"/>
       <c r="I10" s="28"/>
       <c r="J10" s="32"/>
     </row>
     <row r="11" spans="1:10" ht="48" customHeight="1">
-      <c r="A11" s="142" t="s">
-        <v>345</v>
+      <c r="A11" s="158" t="s">
+        <v>364</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C11" s="66">
         <v>1</v>
@@ -10053,20 +10699,24 @@
         <v>614</v>
       </c>
       <c r="E11" s="67" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="G11" s="28"/>
+        <v>367</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
+      <c r="I11" s="28" t="s">
+        <v>368</v>
+      </c>
       <c r="J11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="46.9">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" ht="47.25">
+      <c r="A12" s="158"/>
       <c r="B12" s="62" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C12" s="66">
         <v>1</v>
@@ -10075,20 +10725,24 @@
         <v>1004</v>
       </c>
       <c r="E12" s="67" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="G12" s="28"/>
+        <v>370</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
+      <c r="I12" s="28" t="s">
+        <v>368</v>
+      </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="62.45">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" ht="63">
+      <c r="A13" s="158"/>
       <c r="B13" s="62" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="C13" s="66">
         <v>1</v>
@@ -10097,20 +10751,24 @@
         <v>16</v>
       </c>
       <c r="E13" s="67" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="G13" s="28"/>
+        <v>372</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
+      <c r="I13" s="155" t="s">
+        <v>368</v>
+      </c>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="31.15">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="31.5">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="C14" s="66">
         <v>1</v>
@@ -10119,20 +10777,24 @@
         <v>16</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F14" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="G14" s="28"/>
+        <v>374</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
+      <c r="I14" s="28" t="s">
+        <v>368</v>
+      </c>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" ht="93.6">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" ht="94.5">
+      <c r="A15" s="158"/>
       <c r="B15" s="62" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C15" s="66">
         <v>1</v>
@@ -10141,22 +10803,26 @@
         <v>16</v>
       </c>
       <c r="E15" s="67" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="G15" s="28"/>
+        <v>376</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="I15" s="28" t="s">
+        <v>368</v>
+      </c>
       <c r="J15" s="32"/>
     </row>
     <row r="16" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A16" s="142" t="s">
-        <v>357</v>
+      <c r="A16" s="158" t="s">
+        <v>377</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C16" s="68">
         <v>2</v>
@@ -10165,20 +10831,24 @@
         <v>290</v>
       </c>
       <c r="E16" s="67" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="G16" s="28"/>
+        <v>380</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+      <c r="I16" s="28" t="s">
+        <v>381</v>
+      </c>
       <c r="J16" s="32"/>
     </row>
-    <row r="17" spans="1:10" ht="31.15">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" ht="31.5">
+      <c r="A17" s="158"/>
       <c r="B17" s="62" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C17" s="68">
         <v>2</v>
@@ -10188,17 +10858,23 @@
       </c>
       <c r="E17" s="67"/>
       <c r="F17" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+        <v>383</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="124" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="28" t="s">
+        <v>384</v>
+      </c>
       <c r="J17" s="32"/>
     </row>
-    <row r="18" spans="1:10" ht="46.9">
-      <c r="A18" s="142"/>
+    <row r="18" spans="1:10" ht="236.25">
+      <c r="A18" s="158"/>
       <c r="B18" s="62" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C18" s="68">
         <v>2</v>
@@ -10208,19 +10884,25 @@
       </c>
       <c r="E18" s="67"/>
       <c r="F18" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+        <v>386</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="124" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>387</v>
+      </c>
       <c r="J18" s="32"/>
     </row>
     <row r="19" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A19" s="142" t="s">
-        <v>365</v>
+      <c r="A19" s="158" t="s">
+        <v>388</v>
       </c>
       <c r="B19" s="62" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C19" s="69">
         <v>3</v>
@@ -10229,20 +10911,22 @@
         <v>613</v>
       </c>
       <c r="E19" s="67" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="G19" s="28"/>
+        <v>391</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H19" s="28"/>
       <c r="I19" s="28"/>
       <c r="J19" s="32"/>
     </row>
-    <row r="20" spans="1:10" ht="46.9">
-      <c r="A20" s="142"/>
+    <row r="20" spans="1:10" ht="47.25">
+      <c r="A20" s="158"/>
       <c r="B20" s="62" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C20" s="69">
         <v>3</v>
@@ -10251,22 +10935,24 @@
         <v>613</v>
       </c>
       <c r="E20" s="67" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="F20" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="G20" s="28"/>
+        <v>393</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H20" s="28"/>
       <c r="I20" s="28"/>
       <c r="J20" s="32"/>
     </row>
-    <row r="21" spans="1:10" ht="46.9">
-      <c r="A21" s="1" t="s">
-        <v>371</v>
+    <row r="21" spans="1:10" ht="47.25">
+      <c r="A21" s="2" t="s">
+        <v>394</v>
       </c>
       <c r="B21" s="62" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C21" s="70">
         <v>1</v>
@@ -10276,18 +10962,24 @@
       </c>
       <c r="E21" s="71"/>
       <c r="F21" s="36" t="s">
-        <v>373</v>
-      </c>
-      <c r="G21" s="35"/>
+        <v>396</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>26</v>
+      </c>
       <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
+      <c r="I21" t="s">
+        <v>397</v>
+      </c>
       <c r="J21" s="37"/>
     </row>
     <row r="22" spans="1:10" s="25" customFormat="1">
       <c r="A22" s="58"/>
+      <c r="I22"/>
     </row>
     <row r="23" spans="1:10" s="25" customFormat="1">
       <c r="A23" s="58"/>
+      <c r="I23"/>
     </row>
     <row r="24" spans="1:10" s="25" customFormat="1">
       <c r="A24" s="58"/>
@@ -10306,6 +10998,14 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{471EC67F-2B61-47BA-9FDF-E5A06F4DF03F}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{7E748AEB-011B-4489-A1AB-6FD5A5FEB886}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{65500615-CF4C-4AFA-ADEA-201EDA87E34B}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{6A2E70B9-918B-4944-981D-74A9F336D3A8}"/>
+    <hyperlink ref="H17" r:id="rId5" xr:uid="{2D3BDB16-006B-4DBD-8238-E0031CDE13C7}"/>
+    <hyperlink ref="H18" r:id="rId6" xr:uid="{1FC3733D-E88F-46A5-9FE5-70F19EB95A93}"/>
+  </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -10332,7 +11032,7 @@
     <col min="11" max="1024" width="8.7109375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="76" customFormat="1">
+    <row r="1" spans="1:10" s="76" customFormat="1" ht="37.5">
       <c r="A1" s="40" t="s">
         <v>20</v>
       </c>
@@ -10365,11 +11065,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>374</v>
+      <c r="A2" s="158" t="s">
+        <v>398</v>
       </c>
       <c r="B2" s="77" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -10379,23 +11079,23 @@
       </c>
       <c r="E2" s="49"/>
       <c r="F2" s="48" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="134" t="s">
+      <c r="H2" s="130" t="s">
         <v>52</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="113.25">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="126">
+      <c r="A3" s="158"/>
       <c r="B3" s="77" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -10405,23 +11105,23 @@
       </c>
       <c r="E3" s="28"/>
       <c r="F3" s="29" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="135" t="s">
+      <c r="H3" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="113.25">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="110.25">
+      <c r="A4" s="158"/>
       <c r="B4" s="77" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -10431,23 +11131,23 @@
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="135" t="s">
+      <c r="H4" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="15.6">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="15.75">
+      <c r="A5" s="158"/>
       <c r="B5" s="77" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C5" s="66">
         <v>1</v>
@@ -10466,10 +11166,10 @@
       <c r="I5" s="28"/>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="178.5">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="189">
+      <c r="A6" s="158"/>
       <c r="B6" s="77" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="C6" s="66">
         <v>1</v>
@@ -10479,25 +11179,25 @@
       </c>
       <c r="E6" s="28"/>
       <c r="F6" s="29" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="135" t="s">
+      <c r="H6" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10" ht="79.5" customHeight="1">
-      <c r="A7" s="142" t="s">
-        <v>388</v>
+      <c r="A7" s="158" t="s">
+        <v>412</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C7" s="66">
         <v>1</v>
@@ -10507,19 +11207,19 @@
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="29" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="135"/>
+      <c r="H7" s="124"/>
       <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="64.5">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="63">
+      <c r="A8" s="158"/>
       <c r="B8" s="77" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -10529,25 +11229,25 @@
       </c>
       <c r="E8" s="28"/>
       <c r="F8" s="29" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="135" t="s">
+      <c r="H8" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="J8" s="32"/>
     </row>
     <row r="9" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A9" s="142" t="s">
-        <v>394</v>
+      <c r="A9" s="158" t="s">
+        <v>418</v>
       </c>
       <c r="B9" s="77" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -10557,21 +11257,21 @@
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="29" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H9" s="28"/>
       <c r="I9" s="30" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="96.75">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="94.5">
+      <c r="A10" s="158"/>
       <c r="B10" s="77" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="C10" s="66">
         <v>1</v>
@@ -10581,21 +11281,21 @@
       </c>
       <c r="E10" s="28"/>
       <c r="F10" s="29" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="30" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="62.45">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="63">
+      <c r="A11" s="158"/>
       <c r="B11" s="77" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C11" s="78">
         <v>2</v>
@@ -10605,14 +11305,14 @@
       </c>
       <c r="E11" s="35"/>
       <c r="F11" s="36" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>75</v>
       </c>
       <c r="H11" s="35"/>
       <c r="I11" s="35" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="J11" s="37"/>
     </row>
@@ -10693,11 +11393,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="79.5" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>404</v>
+      <c r="A2" s="158" t="s">
+        <v>428</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C2" s="63">
         <v>1</v>
@@ -10707,23 +11407,19 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="134" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="49" t="s">
-        <v>407</v>
-      </c>
+      <c r="H2" s="130"/>
+      <c r="I2" s="49"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="81">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="94.5">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -10733,23 +11429,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="135" t="s">
+      <c r="H3" s="124" t="s">
         <v>175</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="81">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="78.75">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C4" s="66">
         <v>1</v>
@@ -10759,23 +11455,23 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="135" t="s">
-        <v>413</v>
+      <c r="H4" s="124" t="s">
+        <v>436</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="113.25">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="110.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="C5" s="66">
         <v>1</v>
@@ -10785,23 +11481,23 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="135" t="s">
-        <v>417</v>
+      <c r="H5" s="124" t="s">
+        <v>440</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="46.9">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="47.25">
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="C6" s="66">
         <v>1</v>
@@ -10811,23 +11507,21 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H6" s="28"/>
-      <c r="I6" s="28" t="s">
-        <v>421</v>
-      </c>
+      <c r="I6" s="28"/>
       <c r="J6" s="32"/>
     </row>
     <row r="7" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A7" s="142" t="s">
-        <v>422</v>
+      <c r="A7" s="158" t="s">
+        <v>444</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C7" s="66">
         <v>1</v>
@@ -10837,21 +11531,19 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H7" s="28"/>
-      <c r="I7" s="28" t="s">
-        <v>424</v>
-      </c>
+      <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="32.25">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="31.5">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -10861,23 +11553,23 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="135" t="s">
-        <v>427</v>
+      <c r="H8" s="124" t="s">
+        <v>448</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="31.15">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -10887,21 +11579,19 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H9" s="28"/>
-      <c r="I9" s="28" t="s">
-        <v>430</v>
-      </c>
+      <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="62.45">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="63.75" thickBot="1">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="C10" s="66">
         <v>1</v>
@@ -10911,19 +11601,23 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
+      <c r="H10" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="I10" s="141" t="s">
+        <v>454</v>
+      </c>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="46.9">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="48" thickBot="1">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C11" s="66">
         <v>1</v>
@@ -10933,19 +11627,21 @@
       </c>
       <c r="E11" s="67"/>
       <c r="F11" s="80" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
+      <c r="I11" s="28" t="s">
+        <v>456</v>
+      </c>
       <c r="J11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="64.5">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" ht="63">
+      <c r="A12" s="158"/>
       <c r="B12" s="62" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C12" s="66">
         <v>1</v>
@@ -10955,23 +11651,23 @@
       </c>
       <c r="E12" s="67"/>
       <c r="F12" s="80" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="135" t="s">
-        <v>435</v>
+      <c r="H12" s="124" t="s">
+        <v>453</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="64.5">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" ht="63">
+      <c r="A13" s="158"/>
       <c r="B13" s="62" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C13" s="66">
         <v>1</v>
@@ -10981,23 +11677,23 @@
       </c>
       <c r="E13" s="67"/>
       <c r="F13" s="80" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="135" t="s">
-        <v>435</v>
+      <c r="H13" s="124" t="s">
+        <v>453</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="48.75">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="63">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C14" s="66">
         <v>1</v>
@@ -11007,25 +11703,25 @@
       </c>
       <c r="E14" s="67"/>
       <c r="F14" s="80" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="135" t="s">
-        <v>435</v>
+      <c r="H14" s="124" t="s">
+        <v>453</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="J14" s="32"/>
     </row>
     <row r="15" spans="1:10" ht="126.75" customHeight="1">
-      <c r="A15" s="142" t="s">
-        <v>441</v>
+      <c r="A15" s="158" t="s">
+        <v>463</v>
       </c>
       <c r="B15" s="62" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="C15" s="66">
         <v>1</v>
@@ -11035,7 +11731,7 @@
       </c>
       <c r="E15" s="67"/>
       <c r="F15" s="80" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>75</v>
@@ -11044,10 +11740,10 @@
       <c r="I15" s="28"/>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" ht="78">
-      <c r="A16" s="142"/>
+    <row r="16" spans="1:10" ht="78.75">
+      <c r="A16" s="158"/>
       <c r="B16" s="62" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C16" s="66">
         <v>1</v>
@@ -11057,17 +11753,23 @@
       </c>
       <c r="E16" s="67"/>
       <c r="F16" s="80" t="s">
-        <v>445</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+        <v>467</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>453</v>
+      </c>
+      <c r="I16" s="141" t="s">
+        <v>468</v>
+      </c>
       <c r="J16" s="32"/>
     </row>
-    <row r="17" spans="1:10" ht="62.45">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" ht="63">
+      <c r="A17" s="158"/>
       <c r="B17" s="62" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="C17" s="66">
         <v>1</v>
@@ -11077,19 +11779,19 @@
       </c>
       <c r="E17" s="67"/>
       <c r="F17" s="80" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="I17" s="148"/>
       <c r="J17" s="32"/>
     </row>
-    <row r="18" spans="1:10" ht="194.25">
-      <c r="A18" s="142"/>
+    <row r="18" spans="1:10" ht="189">
+      <c r="A18" s="158"/>
       <c r="B18" s="62" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="C18" s="66">
         <v>1</v>
@@ -11099,21 +11801,23 @@
       </c>
       <c r="E18" s="67"/>
       <c r="F18" s="80" t="s">
-        <v>449</v>
-      </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="135" t="s">
-        <v>450</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>451</v>
+        <v>472</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="124" t="s">
+        <v>473</v>
+      </c>
+      <c r="I18" s="147" t="s">
+        <v>474</v>
       </c>
       <c r="J18" s="32"/>
     </row>
-    <row r="19" spans="1:10" ht="81">
-      <c r="A19" s="142"/>
+    <row r="19" spans="1:10" ht="94.5">
+      <c r="A19" s="158"/>
       <c r="B19" s="62" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="C19" s="66">
         <v>1</v>
@@ -11123,21 +11827,19 @@
       </c>
       <c r="E19" s="67"/>
       <c r="F19" s="80" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="28"/>
-      <c r="I19" s="28" t="s">
-        <v>454</v>
-      </c>
+      <c r="I19" s="28"/>
       <c r="J19" s="32"/>
     </row>
-    <row r="20" spans="1:10" ht="64.5">
-      <c r="A20" s="142"/>
+    <row r="20" spans="1:10" ht="63">
+      <c r="A20" s="158"/>
       <c r="B20" s="62" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="C20" s="66">
         <v>1</v>
@@ -11147,21 +11849,19 @@
       </c>
       <c r="E20" s="67"/>
       <c r="F20" s="80" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="G20" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="28"/>
-      <c r="I20" s="28" t="s">
-        <v>457</v>
-      </c>
+      <c r="I20" s="28"/>
       <c r="J20" s="32"/>
     </row>
-    <row r="21" spans="1:10" ht="64.5">
-      <c r="A21" s="142"/>
+    <row r="21" spans="1:10" ht="78.75">
+      <c r="A21" s="158"/>
       <c r="B21" s="62" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="C21" s="66">
         <v>1</v>
@@ -11171,21 +11871,19 @@
       </c>
       <c r="E21" s="67"/>
       <c r="F21" s="80" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H21" s="28"/>
-      <c r="I21" s="28" t="s">
-        <v>460</v>
-      </c>
+      <c r="I21" s="28"/>
       <c r="J21" s="32"/>
     </row>
-    <row r="22" spans="1:10" ht="81">
-      <c r="A22" s="142"/>
+    <row r="22" spans="1:10" ht="78.75">
+      <c r="A22" s="158"/>
       <c r="B22" s="62" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="C22" s="66">
         <v>1</v>
@@ -11195,21 +11893,19 @@
       </c>
       <c r="E22" s="67"/>
       <c r="F22" s="80" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="G22" s="28" t="s">
         <v>75</v>
       </c>
       <c r="H22" s="28"/>
-      <c r="I22" s="28" t="s">
-        <v>463</v>
-      </c>
+      <c r="I22" s="28"/>
       <c r="J22" s="32"/>
     </row>
-    <row r="23" spans="1:10" ht="32.25">
-      <c r="A23" s="142"/>
+    <row r="23" spans="1:10" ht="31.5">
+      <c r="A23" s="158"/>
       <c r="B23" s="62" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="C23" s="66">
         <v>1</v>
@@ -11219,23 +11915,23 @@
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="80" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="135" t="s">
-        <v>435</v>
+      <c r="H23" s="124" t="s">
+        <v>453</v>
       </c>
       <c r="I23" s="28" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="J23" s="32"/>
     </row>
-    <row r="24" spans="1:10" ht="48.75">
-      <c r="A24" s="142"/>
+    <row r="24" spans="1:10" ht="47.25">
+      <c r="A24" s="158"/>
       <c r="B24" s="62" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="C24" s="66">
         <v>1</v>
@@ -11245,19 +11941,25 @@
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="80" t="s">
-        <v>468</v>
-      </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
+        <v>487</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>488</v>
+      </c>
       <c r="J24" s="32"/>
     </row>
     <row r="25" spans="1:10" ht="48" customHeight="1">
-      <c r="A25" s="142" t="s">
-        <v>469</v>
+      <c r="A25" s="158" t="s">
+        <v>489</v>
       </c>
       <c r="B25" s="62" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="C25" s="68">
         <v>2</v>
@@ -11267,16 +11969,21 @@
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="80" t="s">
-        <v>471</v>
+        <v>491</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="I25" s="30" t="s">
+        <v>492</v>
+      </c>
       <c r="J25" s="32"/>
     </row>
-    <row r="26" spans="1:10" ht="32.25">
-      <c r="A26" s="142"/>
+    <row r="26" spans="1:10" ht="31.5">
+      <c r="A26" s="158"/>
       <c r="B26" s="62" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="C26" s="68">
         <v>2</v>
@@ -11286,7 +11993,7 @@
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="80" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="G26" s="28" t="s">
         <v>75</v>
@@ -11295,10 +12002,10 @@
       <c r="I26" s="28"/>
       <c r="J26" s="32"/>
     </row>
-    <row r="27" spans="1:10" ht="32.25">
-      <c r="A27" s="142"/>
+    <row r="27" spans="1:10" ht="31.5">
+      <c r="A27" s="158"/>
       <c r="B27" s="62" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="C27" s="68">
         <v>2</v>
@@ -11308,7 +12015,7 @@
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="80" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="G27" s="28" t="s">
         <v>75</v>
@@ -11317,12 +12024,12 @@
       <c r="I27" s="28"/>
       <c r="J27" s="32"/>
     </row>
-    <row r="28" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A28" s="142" t="s">
-        <v>476</v>
+    <row r="28" spans="1:10" ht="63.75" customHeight="1" thickBot="1">
+      <c r="A28" s="158" t="s">
+        <v>497</v>
       </c>
       <c r="B28" s="62" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="C28" s="66">
         <v>1</v>
@@ -11332,23 +12039,23 @@
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="80" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="G28" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="135" t="s">
+      <c r="H28" s="124" t="s">
         <v>52</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="J28" s="32"/>
     </row>
-    <row r="29" spans="1:10" ht="64.5">
-      <c r="A29" s="142"/>
+    <row r="29" spans="1:10" ht="63.75" thickBot="1">
+      <c r="A29" s="158"/>
       <c r="B29" s="62" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="C29" s="66">
         <v>1</v>
@@ -11358,17 +12065,23 @@
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="80" t="s">
-        <v>481</v>
-      </c>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+        <v>502</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="I29" s="141" t="s">
+        <v>503</v>
+      </c>
       <c r="J29" s="32"/>
     </row>
-    <row r="30" spans="1:10" ht="46.9">
-      <c r="A30" s="142"/>
+    <row r="30" spans="1:10" ht="48" thickBot="1">
+      <c r="A30" s="158"/>
       <c r="B30" s="62" t="s">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="C30" s="66">
         <v>1</v>
@@ -11378,17 +12091,23 @@
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="80" t="s">
-        <v>483</v>
-      </c>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+        <v>505</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="124" t="s">
+        <v>268</v>
+      </c>
+      <c r="I30" s="141" t="s">
+        <v>506</v>
+      </c>
       <c r="J30" s="32"/>
     </row>
-    <row r="31" spans="1:10" ht="46.9">
-      <c r="A31" s="142"/>
+    <row r="31" spans="1:10" ht="48" thickBot="1">
+      <c r="A31" s="158"/>
       <c r="B31" s="62" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="C31" s="70">
         <v>1</v>
@@ -11398,15 +12117,13 @@
       </c>
       <c r="E31" s="34"/>
       <c r="F31" s="81" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="H31" s="35"/>
-      <c r="I31" s="35" t="s">
-        <v>486</v>
-      </c>
+      <c r="I31" s="35"/>
       <c r="J31" s="37"/>
     </row>
   </sheetData>
@@ -11418,23 +12135,25 @@
     <mergeCell ref="A28:A31"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G24 G26:G31 H25" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G31 H25" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Valid,Non-valid,Not Applicable"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{E2CAAF3F-D07A-494C-AE8E-45E2CF522008}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{F3164F80-3CA2-4A67-A31A-065FED63672C}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{B7852959-4F45-47AE-8DDA-002C600A4AE1}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{BFB94FB0-972D-455F-89BC-1CDA24BDAD96}"/>
-    <hyperlink ref="H8" r:id="rId5" xr:uid="{247F1544-5085-4191-9B83-E8E8CA43F5AB}"/>
-    <hyperlink ref="H12" r:id="rId6" xr:uid="{D1D044A0-620D-40E0-9C12-23FCA50069B3}"/>
-    <hyperlink ref="H13" r:id="rId7" xr:uid="{55A196CD-24DF-4632-9C46-8F1B6F024CAF}"/>
-    <hyperlink ref="H14" r:id="rId8" xr:uid="{6B239A0E-9C1E-4B47-8A1B-FC5958E11DFA}"/>
-    <hyperlink ref="H18" r:id="rId9" xr:uid="{F05A50E1-6EBB-4B81-842D-9F45F3F70440}"/>
-    <hyperlink ref="H23" r:id="rId10" xr:uid="{904F8DC2-9CFC-4885-AA22-6D7B4C78C887}"/>
-    <hyperlink ref="H28" r:id="rId11" xr:uid="{265A6AA4-F840-4516-B1C9-1B6F6996B063}"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{F3164F80-3CA2-4A67-A31A-065FED63672C}"/>
+    <hyperlink ref="H4" r:id="rId2" xr:uid="{B7852959-4F45-47AE-8DDA-002C600A4AE1}"/>
+    <hyperlink ref="H5" r:id="rId3" xr:uid="{BFB94FB0-972D-455F-89BC-1CDA24BDAD96}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{247F1544-5085-4191-9B83-E8E8CA43F5AB}"/>
+    <hyperlink ref="H12" r:id="rId5" xr:uid="{D1D044A0-620D-40E0-9C12-23FCA50069B3}"/>
+    <hyperlink ref="H13" r:id="rId6" xr:uid="{55A196CD-24DF-4632-9C46-8F1B6F024CAF}"/>
+    <hyperlink ref="H14" r:id="rId7" xr:uid="{6B239A0E-9C1E-4B47-8A1B-FC5958E11DFA}"/>
+    <hyperlink ref="H18" r:id="rId8" xr:uid="{F05A50E1-6EBB-4B81-842D-9F45F3F70440}"/>
+    <hyperlink ref="H23" r:id="rId9" xr:uid="{904F8DC2-9CFC-4885-AA22-6D7B4C78C887}"/>
+    <hyperlink ref="H28" r:id="rId10" xr:uid="{265A6AA4-F840-4516-B1C9-1B6F6996B063}"/>
+    <hyperlink ref="H24" r:id="rId11" xr:uid="{EBF72114-C899-8A44-9ACE-6F730C1FDB0E}"/>
+    <hyperlink ref="H29" r:id="rId12" xr:uid="{A5453578-CC95-B74F-A13C-321AA4BED1AF}"/>
+    <hyperlink ref="H30" r:id="rId13" xr:uid="{4D3F1929-265A-194B-85A6-D30FE6E1D60E}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11495,11 +12214,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>487</v>
+      <c r="A2" s="158" t="s">
+        <v>509</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="C2" s="82">
         <v>2</v>
@@ -11509,17 +12228,23 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>489</v>
-      </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
+        <v>511</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="50" t="s">
+        <v>512</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>513</v>
+      </c>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="31.15">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="31.5">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="C3" s="68">
         <v>2</v>
@@ -11529,17 +12254,19 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>491</v>
-      </c>
-      <c r="G3" s="28"/>
+        <v>515</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H3" s="28"/>
       <c r="I3" s="28"/>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="46.9">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="48" thickBot="1">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C4" s="68">
         <v>2</v>
@@ -11549,19 +12276,21 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>492</v>
-      </c>
-      <c r="G4" s="28"/>
+        <v>516</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H4" s="28"/>
       <c r="I4" s="28"/>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A5" s="142" t="s">
-        <v>493</v>
+    <row r="5" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A5" s="158" t="s">
+        <v>517</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="C5" s="66">
         <v>1</v>
@@ -11571,17 +12300,23 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>495</v>
-      </c>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+        <v>519</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>520</v>
+      </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="46.9">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="103.5" thickBot="1">
+      <c r="A6" s="158"/>
       <c r="B6" s="62" t="s">
-        <v>496</v>
+        <v>521</v>
       </c>
       <c r="C6" s="68">
         <v>2</v>
@@ -11591,17 +12326,23 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>497</v>
-      </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
+        <v>522</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="151" t="s">
+        <v>523</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>524</v>
+      </c>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="31.15">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="409.6" thickBot="1">
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="C7" s="68">
         <v>2</v>
@@ -11611,17 +12352,23 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>499</v>
-      </c>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
+        <v>526</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>527</v>
+      </c>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="46.9">
-      <c r="A8" s="142"/>
+    <row r="8" spans="1:10" ht="282" thickBot="1">
+      <c r="A8" s="158"/>
       <c r="B8" s="62" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="C8" s="68">
         <v>2</v>
@@ -11631,17 +12378,23 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>501</v>
-      </c>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
+        <v>529</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="123" t="s">
+        <v>530</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>531</v>
+      </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="46.9">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="48" thickBot="1">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="C9" s="68">
         <v>2</v>
@@ -11651,17 +12404,23 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>503</v>
-      </c>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
+        <v>533</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="124" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>534</v>
+      </c>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="46.9">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="48" thickBot="1">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="C10" s="68">
         <v>2</v>
@@ -11671,17 +12430,23 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>505</v>
-      </c>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
+        <v>536</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>537</v>
+      </c>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="31.15">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="331.5" thickBot="1">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="C11" s="69">
         <v>3</v>
@@ -11691,17 +12456,23 @@
       </c>
       <c r="E11" s="67"/>
       <c r="F11" s="80" t="s">
-        <v>507</v>
-      </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
+        <v>539</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>541</v>
+      </c>
       <c r="J11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="31.15">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A12" s="158"/>
       <c r="B12" s="62" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="C12" s="69">
         <v>3</v>
@@ -11711,19 +12482,25 @@
       </c>
       <c r="E12" s="67"/>
       <c r="F12" s="80" t="s">
-        <v>509</v>
-      </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
+        <v>543</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>544</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>545</v>
+      </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="48" customHeight="1">
-      <c r="A13" s="142" t="s">
-        <v>510</v>
+    <row r="13" spans="1:10" ht="48" customHeight="1" thickBot="1">
+      <c r="A13" s="158" t="s">
+        <v>546</v>
       </c>
       <c r="B13" s="62" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="C13" s="68">
         <v>2</v>
@@ -11733,17 +12510,23 @@
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="80" t="s">
-        <v>512</v>
-      </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
+        <v>548</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>550</v>
+      </c>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="46.9">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="48" thickBot="1">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="C14" s="68">
         <v>2</v>
@@ -11753,17 +12536,21 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="80" t="s">
-        <v>514</v>
-      </c>
-      <c r="G14" s="28"/>
+        <v>552</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
+      <c r="I14" s="28" t="s">
+        <v>553</v>
+      </c>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" ht="31.15">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A15" s="158"/>
       <c r="B15" s="62" t="s">
-        <v>515</v>
+        <v>554</v>
       </c>
       <c r="C15" s="69">
         <v>3</v>
@@ -11773,19 +12560,25 @@
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="80" t="s">
-        <v>516</v>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+        <v>555</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>556</v>
+      </c>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" ht="48" customHeight="1">
-      <c r="A16" s="142" t="s">
-        <v>517</v>
+    <row r="16" spans="1:10" ht="48" customHeight="1" thickBot="1">
+      <c r="A16" s="158" t="s">
+        <v>557</v>
       </c>
       <c r="B16" s="62" t="s">
-        <v>518</v>
+        <v>558</v>
       </c>
       <c r="C16" s="68">
         <v>2</v>
@@ -11795,17 +12588,23 @@
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="80" t="s">
-        <v>519</v>
-      </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+        <v>559</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="124" t="s">
+        <v>560</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>561</v>
+      </c>
       <c r="J16" s="32"/>
     </row>
-    <row r="17" spans="1:10" ht="46.9">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" ht="48" thickBot="1">
+      <c r="A17" s="158"/>
       <c r="B17" s="62" t="s">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="C17" s="78">
         <v>2</v>
@@ -11815,9 +12614,11 @@
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="81" t="s">
-        <v>521</v>
-      </c>
-      <c r="G17" s="35"/>
+        <v>563</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>112</v>
+      </c>
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
       <c r="J17" s="37"/>
@@ -11835,8 +12636,14 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" r:id="rId1" xr:uid="{41B824DD-5EEA-46D7-86EA-FD1FF40D1325}"/>
+    <hyperlink ref="H9" r:id="rId2" xr:uid="{5E2FED62-6556-421D-8B57-F656A0819752}"/>
+    <hyperlink ref="H8" r:id="rId3" display="https://github.com/IsepMartimOliveira/desofs2025_wed_ffs_4/blob/main/src/main/java/com/example/psoft_22_23_project/configuration/SecurityConfig.java @Bean_x000a__x0009_public JwtEncoder jwtEncoder() {_x000a__x0009__x0009_final JWK jwk = new RSAKey.Builder(this.rsaPublicKey).privateKey(this.rsaPrivateKey).build();_x000a__x0009__x0009_final JWKSource&lt;SecurityContext&gt; jwks = new ImmutableJWKSet&lt;&gt;(new JWKSet(jwk));_x000a__x0009__x0009_return new NimbusJwtEncoder(jwks);_x000a__x0009_}_x000a__x000a__x0009_// Used by JwtAuthenticationProvider to decode and validate JWT tokens_x000a__x0009_@Bean_x000a__x0009_public JwtDecoder jwtDecoder() {_x000a__x0009__x0009_return NimbusJwtDecoder.withPublicKey(this.rsaPublicKey).build();_x000a__x0009_}" xr:uid="{C5354010-139E-4B70-9005-EE42A5D3DA5F}"/>
+    <hyperlink ref="H6" r:id="rId4" xr:uid="{5274CCD4-CBAB-4081-83B0-D57E3EAE1057}"/>
+  </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -11894,11 +12701,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>522</v>
+      <c r="A2" s="158" t="s">
+        <v>564</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C2" s="88">
         <v>1</v>
@@ -11908,23 +12715,23 @@
       </c>
       <c r="E2" s="90"/>
       <c r="F2" s="91" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
       <c r="G2" s="92" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="129" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I2" s="92" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="J2" s="93"/>
     </row>
-    <row r="3" spans="1:10" ht="46.9">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="47.25">
+      <c r="A3" s="158"/>
       <c r="B3" s="62" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="C3" s="66">
         <v>1</v>
@@ -11934,23 +12741,23 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="124" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="62.45">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="63">
+      <c r="A4" s="158"/>
       <c r="B4" s="62" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="C4" s="68">
         <v>2</v>
@@ -11960,23 +12767,23 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="124" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="46.9">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="47.25">
+      <c r="A5" s="158"/>
       <c r="B5" s="62" t="s">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="C5" s="68">
         <v>2</v>
@@ -11986,25 +12793,25 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="G5" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="J5" s="32"/>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1">
-      <c r="A6" s="142" t="s">
-        <v>534</v>
+      <c r="A6" s="158" t="s">
+        <v>575</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C6" s="68">
         <v>2</v>
@@ -12014,23 +12821,23 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="124" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="46.9">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="47.25">
+      <c r="A7" s="158"/>
       <c r="B7" s="62" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="C7" s="68">
         <v>2</v>
@@ -12040,25 +12847,25 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="124" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:10" ht="48" customHeight="1">
-      <c r="A8" s="142" t="s">
-        <v>539</v>
+      <c r="A8" s="158" t="s">
+        <v>580</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="C8" s="68">
         <v>2</v>
@@ -12068,23 +12875,23 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>543</v>
+        <v>584</v>
       </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="15.6">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="15.75">
+      <c r="A9" s="158"/>
       <c r="B9" s="62" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="C9" s="68">
         <v>2</v>
@@ -12094,7 +12901,7 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
@@ -12103,10 +12910,10 @@
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="31.15">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="31.5">
+      <c r="A10" s="158"/>
       <c r="B10" s="62" t="s">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="C10" s="68">
         <v>2</v>
@@ -12116,7 +12923,7 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>75</v>
@@ -12125,10 +12932,10 @@
       <c r="I10" s="28"/>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="62.45">
-      <c r="A11" s="142"/>
+    <row r="11" spans="1:10" ht="63">
+      <c r="A11" s="158"/>
       <c r="B11" s="62" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="C11" s="68">
         <v>2</v>
@@ -12136,7 +12943,7 @@
       <c r="D11" s="27"/>
       <c r="E11" s="67"/>
       <c r="F11" s="80" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>75</v>
@@ -12146,11 +12953,11 @@
       <c r="J11" s="32"/>
     </row>
     <row r="12" spans="1:10" ht="63.75" customHeight="1">
-      <c r="A12" s="142" t="s">
-        <v>550</v>
+      <c r="A12" s="158" t="s">
+        <v>591</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="C12" s="66">
         <v>1</v>
@@ -12160,23 +12967,23 @@
       </c>
       <c r="E12" s="67"/>
       <c r="F12" s="80" t="s">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="46.9">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" ht="47.25">
+      <c r="A13" s="158"/>
       <c r="B13" s="62" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="C13" s="68">
         <v>2</v>
@@ -12186,23 +12993,23 @@
       </c>
       <c r="E13" s="67"/>
       <c r="F13" s="80" t="s">
-        <v>555</v>
+        <v>596</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="46.9">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="47.25">
+      <c r="A14" s="158"/>
       <c r="B14" s="62" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="C14" s="78">
         <v>2</v>
@@ -12212,16 +13019,16 @@
       </c>
       <c r="E14" s="71"/>
       <c r="F14" s="81" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>26</v>
       </c>
       <c r="H14" s="132" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="J14" s="37"/>
     </row>
@@ -12271,7 +13078,7 @@
     <col min="11" max="1024" width="8.7109375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="43" customFormat="1" ht="42">
+    <row r="1" spans="1:10" s="43" customFormat="1" ht="42.75" thickBot="1">
       <c r="A1" s="94" t="s">
         <v>20</v>
       </c>
@@ -12303,12 +13110,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A2" s="142" t="s">
-        <v>559</v>
+    <row r="2" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A2" s="159" t="s">
+        <v>600</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="C2" s="82">
         <v>2</v>
@@ -12318,7 +13125,7 @@
       </c>
       <c r="E2" s="64"/>
       <c r="F2" s="79" t="s">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="G2" s="49" t="s">
         <v>75</v>
@@ -12327,10 +13134,10 @@
       <c r="I2" s="49"/>
       <c r="J2" s="65"/>
     </row>
-    <row r="3" spans="1:10" ht="46.9">
-      <c r="A3" s="142"/>
+    <row r="3" spans="1:10" ht="48" thickBot="1">
+      <c r="A3" s="160"/>
       <c r="B3" s="62" t="s">
-        <v>562</v>
+        <v>603</v>
       </c>
       <c r="C3" s="68">
         <v>2</v>
@@ -12340,7 +13147,7 @@
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="80" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="G3" s="28" t="s">
         <v>75</v>
@@ -12349,10 +13156,10 @@
       <c r="I3" s="28"/>
       <c r="J3" s="32"/>
     </row>
-    <row r="4" spans="1:10" ht="31.15">
-      <c r="A4" s="142"/>
+    <row r="4" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A4" s="160"/>
       <c r="B4" s="62" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="C4" s="68">
         <v>2</v>
@@ -12362,19 +13169,23 @@
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="80" t="s">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="G4" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
+      <c r="H4" s="28" t="s">
+        <v>607</v>
+      </c>
+      <c r="I4" s="141" t="s">
+        <v>608</v>
+      </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="1:10" ht="31.15">
-      <c r="A5" s="142"/>
+    <row r="5" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A5" s="160"/>
       <c r="B5" s="62" t="s">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="C5" s="68">
         <v>2</v>
@@ -12384,19 +13195,23 @@
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="80" t="s">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="141" t="s">
+        <v>611</v>
+      </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" ht="31.15">
-      <c r="A6" s="142"/>
+    <row r="6" spans="1:10" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A6" s="160"/>
       <c r="B6" s="62" t="s">
-        <v>568</v>
+        <v>612</v>
       </c>
       <c r="C6" s="69">
         <v>3</v>
@@ -12406,7 +13221,7 @@
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="80" t="s">
-        <v>569</v>
+        <v>613</v>
       </c>
       <c r="G6" s="28" t="s">
         <v>75</v>
@@ -12415,10 +13230,10 @@
       <c r="I6" s="28"/>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" ht="15.6">
-      <c r="A7" s="142"/>
+    <row r="7" spans="1:10" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A7" s="161"/>
       <c r="B7" s="62" t="s">
-        <v>570</v>
+        <v>614</v>
       </c>
       <c r="C7" s="69">
         <v>3</v>
@@ -12428,7 +13243,7 @@
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="80" t="s">
-        <v>571</v>
+        <v>615</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>75</v>
@@ -12437,12 +13252,12 @@
       <c r="I7" s="28"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A8" s="142" t="s">
-        <v>572</v>
+    <row r="8" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A8" s="159" t="s">
+        <v>616</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>573</v>
+        <v>617</v>
       </c>
       <c r="C8" s="66">
         <v>1</v>
@@ -12452,17 +13267,19 @@
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="80" t="s">
-        <v>574</v>
-      </c>
-      <c r="G8" s="28"/>
+        <v>618</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>75</v>
+      </c>
       <c r="H8" s="28"/>
       <c r="I8" s="28"/>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="1:10" ht="31.15">
-      <c r="A9" s="142"/>
+    <row r="9" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A9" s="160"/>
       <c r="B9" s="62" t="s">
-        <v>575</v>
+        <v>619</v>
       </c>
       <c r="C9" s="66">
         <v>1</v>
@@ -12472,7 +13289,7 @@
       </c>
       <c r="E9" s="67"/>
       <c r="F9" s="80" t="s">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>75</v>
@@ -12481,10 +13298,10 @@
       <c r="I9" s="28"/>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="1:10" ht="31.15">
-      <c r="A10" s="142"/>
+    <row r="10" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A10" s="161"/>
       <c r="B10" s="62" t="s">
-        <v>577</v>
+        <v>621</v>
       </c>
       <c r="C10" s="66">
         <v>1</v>
@@ -12494,7 +13311,7 @@
       </c>
       <c r="E10" s="67"/>
       <c r="F10" s="80" t="s">
-        <v>578</v>
+        <v>622</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>75</v>
@@ -12503,12 +13320,12 @@
       <c r="I10" s="28"/>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A11" s="142" t="s">
-        <v>579</v>
+    <row r="11" spans="1:10" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A11" s="159" t="s">
+        <v>623</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="C11" s="66">
         <v>1</v>
@@ -12518,7 +13335,7 @@
       </c>
       <c r="E11" s="67"/>
       <c r="F11" s="80" t="s">
-        <v>581</v>
+        <v>625</v>
       </c>
       <c r="G11" s="28" t="s">
         <v>75</v>
@@ -12527,10 +13344,10 @@
       <c r="I11" s="28"/>
       <c r="J11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="16.5">
-      <c r="A12" s="142"/>
+    <row r="12" spans="1:10" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A12" s="160"/>
       <c r="B12" s="62" t="s">
-        <v>582</v>
+        <v>626</v>
       </c>
       <c r="C12" s="66">
         <v>1</v>
@@ -12540,7 +13357,7 @@
       </c>
       <c r="E12" s="67"/>
       <c r="F12" s="80" t="s">
-        <v>583</v>
+        <v>627</v>
       </c>
       <c r="G12" s="28" t="s">
         <v>26</v>
@@ -12549,14 +13366,14 @@
         <v>187</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>584</v>
+        <v>628</v>
       </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" ht="46.9">
-      <c r="A13" s="142"/>
+    <row r="13" spans="1:10" ht="48" thickBot="1">
+      <c r="A13" s="160"/>
       <c r="B13" s="62" t="s">
-        <v>585</v>
+        <v>629</v>
       </c>
       <c r="C13" s="66">
         <v>1</v>
@@ -12566,7 +13383,7 @@
       </c>
       <c r="E13" s="67"/>
       <c r="F13" s="80" t="s">
-        <v>586</v>
+        <v>630</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>75</v>
@@ -12575,10 +13392,10 @@
       <c r="I13" s="28"/>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="1:10" ht="46.9">
-      <c r="A14" s="142"/>
+    <row r="14" spans="1:10" ht="48" thickBot="1">
+      <c r="A14" s="160"/>
       <c r="B14" s="62" t="s">
-        <v>587</v>
+        <v>631</v>
       </c>
       <c r="C14" s="66">
         <v>1</v>
@@ -12588,19 +13405,23 @@
       </c>
       <c r="E14" s="67"/>
       <c r="F14" s="80" t="s">
-        <v>588</v>
+        <v>632</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
+      <c r="H14" s="140" t="s">
+        <v>242</v>
+      </c>
+      <c r="I14" s="140" t="s">
+        <v>242</v>
+      </c>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" ht="31.15">
-      <c r="A15" s="142"/>
+    <row r="15" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A15" s="160"/>
       <c r="B15" s="62" t="s">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="C15" s="68">
         <v>2</v>
@@ -12610,19 +13431,23 @@
       </c>
       <c r="E15" s="67"/>
       <c r="F15" s="80" t="s">
-        <v>590</v>
+        <v>634</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="H15" s="141" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="141" t="s">
+        <v>242</v>
+      </c>
       <c r="J15" s="32"/>
     </row>
-    <row r="16" spans="1:10" ht="31.15">
-      <c r="A16" s="142"/>
+    <row r="16" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A16" s="160"/>
       <c r="B16" s="62" t="s">
-        <v>591</v>
+        <v>635</v>
       </c>
       <c r="C16" s="68">
         <v>2</v>
@@ -12632,19 +13457,23 @@
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="80" t="s">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="H16" s="141" t="s">
+        <v>210</v>
+      </c>
+      <c r="I16" s="141" t="s">
+        <v>210</v>
+      </c>
       <c r="J16" s="32"/>
     </row>
-    <row r="17" spans="1:10" ht="46.9">
-      <c r="A17" s="142"/>
+    <row r="17" spans="1:10" ht="48" thickBot="1">
+      <c r="A17" s="160"/>
       <c r="B17" s="62" t="s">
-        <v>593</v>
+        <v>637</v>
       </c>
       <c r="C17" s="68">
         <v>2</v>
@@ -12654,19 +13483,23 @@
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="80" t="s">
-        <v>594</v>
+        <v>638</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="H17" s="141" t="s">
+        <v>639</v>
+      </c>
+      <c r="I17" s="141" t="s">
+        <v>639</v>
+      </c>
       <c r="J17" s="32"/>
     </row>
-    <row r="18" spans="1:10" ht="31.15">
-      <c r="A18" s="142"/>
+    <row r="18" spans="1:10" ht="32.25" thickBot="1">
+      <c r="A18" s="161"/>
       <c r="B18" s="62" t="s">
-        <v>595</v>
+        <v>640</v>
       </c>
       <c r="C18" s="78">
         <v>2</v>
@@ -12676,13 +13509,17 @@
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="81" t="s">
-        <v>596</v>
+        <v>641</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
+        <v>26</v>
+      </c>
+      <c r="H18" s="141" t="s">
+        <v>242</v>
+      </c>
+      <c r="I18" s="141" t="s">
+        <v>242</v>
+      </c>
       <c r="J18" s="37"/>
     </row>
   </sheetData>
@@ -12710,6 +13547,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100701532D62E64B542897B015DD7EB8BE1" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b7a3569226b74d60e6b652ffc71f4d32">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="fc394eac-1db9-4ed7-841e-dbad75f37114" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="703ca15fe0f30b5d272d860e07a56b87" ns3:_="">
     <xsd:import namespace="fc394eac-1db9-4ed7-841e-dbad75f37114"/>
@@ -12859,15 +13705,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -12875,11 +13712,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D146C6-1B40-4037-981A-C1EEC2FA8E42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A6ED93-0A8E-4261-94B4-DEC66AFC9D40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0A6ED93-0A8E-4261-94B4-DEC66AFC9D40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D146C6-1B40-4037-981A-C1EEC2FA8E42}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
